--- a/РАБОЧИЙ СТОЛ/расчеты Останкино КИ/Донецк/Дв.Останкино Колбаса от 22,06,26, Донецк (согласовал Лыгин).xlsx
+++ b/РАБОЧИЙ СТОЛ/расчеты Останкино КИ/Донецк/Дв.Останкино Колбаса от 22,06,26, Донецк (согласовал Лыгин).xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\06,26\24,06,26 Останкино КИ\КИ + ЗПФ\Донецк\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ\Донецк\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D563FAC-677E-498E-BCB1-CD6EF0F57D78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52AD2AE8-5BD7-4065-BB1D-4C232C78A072}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <externalReference r:id="rId3"/>
     <externalReference r:id="rId4"/>
   </externalReferences>
-  <calcPr calcId="191029" refMode="R1C1"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -609,7 +609,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -708,7 +708,6 @@
     <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
@@ -14455,7 +14454,7 @@
         <f t="shared" si="1"/>
         <v>5309.6044000000011</v>
       </c>
-      <c r="S10" s="44">
+      <c r="S10" s="20">
         <f t="shared" si="1"/>
         <v>20284</v>
       </c>
@@ -14557,7 +14556,7 @@
         <f>F11/5</f>
         <v>76.400000000000006</v>
       </c>
-      <c r="S11" s="45">
+      <c r="S11" s="44">
         <v>540</v>
       </c>
       <c r="T11" s="23">
@@ -14716,7 +14715,7 @@
         <f t="shared" ref="R12:R75" si="4">F12/5</f>
         <v>1.9655999999999998</v>
       </c>
-      <c r="S12" s="45">
+      <c r="S12" s="44">
         <v>20</v>
       </c>
       <c r="T12" s="23">
@@ -14877,7 +14876,7 @@
         <f t="shared" si="4"/>
         <v>45.8</v>
       </c>
-      <c r="S13" s="45"/>
+      <c r="S13" s="44"/>
       <c r="T13" s="23">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -15036,7 +15035,7 @@
         <f t="shared" si="4"/>
         <v>273.19079999999997</v>
       </c>
-      <c r="S14" s="45">
+      <c r="S14" s="44">
         <v>1300</v>
       </c>
       <c r="T14" s="23">
@@ -15196,7 +15195,7 @@
         <f t="shared" si="4"/>
         <v>6.8614000000000006</v>
       </c>
-      <c r="S15" s="45">
+      <c r="S15" s="44">
         <v>60</v>
       </c>
       <c r="T15" s="23">
@@ -15357,7 +15356,7 @@
         <f t="shared" si="4"/>
         <v>36.8416</v>
       </c>
-      <c r="S16" s="45">
+      <c r="S16" s="44">
         <v>180</v>
       </c>
       <c r="T16" s="23">
@@ -15518,7 +15517,7 @@
         <f t="shared" si="4"/>
         <v>103.453</v>
       </c>
-      <c r="S17" s="45">
+      <c r="S17" s="44">
         <v>580</v>
       </c>
       <c r="T17" s="23">
@@ -15679,7 +15678,7 @@
         <f t="shared" si="4"/>
         <v>20.097200000000001</v>
       </c>
-      <c r="S18" s="45">
+      <c r="S18" s="44">
         <v>150</v>
       </c>
       <c r="T18" s="23">
@@ -15840,7 +15839,7 @@
         <f t="shared" si="4"/>
         <v>13.082800000000001</v>
       </c>
-      <c r="S19" s="45">
+      <c r="S19" s="44">
         <v>80</v>
       </c>
       <c r="T19" s="23">
@@ -16001,7 +16000,7 @@
         <f t="shared" si="4"/>
         <v>13.6</v>
       </c>
-      <c r="S20" s="45"/>
+      <c r="S20" s="44"/>
       <c r="T20" s="23">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -16160,7 +16159,7 @@
         <f t="shared" si="4"/>
         <v>90.4</v>
       </c>
-      <c r="S21" s="45">
+      <c r="S21" s="44">
         <v>330</v>
       </c>
       <c r="T21" s="23">
@@ -16321,7 +16320,7 @@
         <f t="shared" si="4"/>
         <v>76.385400000000004</v>
       </c>
-      <c r="S22" s="45">
+      <c r="S22" s="44">
         <v>230</v>
       </c>
       <c r="T22" s="23">
@@ -16480,7 +16479,7 @@
         <f t="shared" si="4"/>
         <v>0.68220000000000003</v>
       </c>
-      <c r="S23" s="45"/>
+      <c r="S23" s="44"/>
       <c r="T23" s="23">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -16639,7 +16638,7 @@
         <f t="shared" si="4"/>
         <v>56.6</v>
       </c>
-      <c r="S24" s="45"/>
+      <c r="S24" s="44"/>
       <c r="T24" s="23">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -16798,7 +16797,7 @@
         <f t="shared" si="4"/>
         <v>68.502600000000001</v>
       </c>
-      <c r="S25" s="45">
+      <c r="S25" s="44">
         <v>490</v>
       </c>
       <c r="T25" s="23">
@@ -16959,7 +16958,7 @@
         <f t="shared" si="4"/>
         <v>44</v>
       </c>
-      <c r="S26" s="45">
+      <c r="S26" s="44">
         <v>430</v>
       </c>
       <c r="T26" s="23">
@@ -17118,7 +17117,7 @@
         <f t="shared" si="4"/>
         <v>2.2000000000000002</v>
       </c>
-      <c r="S27" s="45"/>
+      <c r="S27" s="44"/>
       <c r="T27" s="23">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -17277,7 +17276,7 @@
         <f t="shared" si="4"/>
         <v>72.2042</v>
       </c>
-      <c r="S28" s="45">
+      <c r="S28" s="44">
         <v>650</v>
       </c>
       <c r="T28" s="23">
@@ -17438,7 +17437,7 @@
         <f t="shared" si="4"/>
         <v>88.8</v>
       </c>
-      <c r="S29" s="45">
+      <c r="S29" s="44">
         <v>690</v>
       </c>
       <c r="T29" s="23">
@@ -17599,7 +17598,7 @@
         <f t="shared" si="4"/>
         <v>40.799999999999997</v>
       </c>
-      <c r="S30" s="45">
+      <c r="S30" s="44">
         <v>500</v>
       </c>
       <c r="T30" s="23">
@@ -17760,7 +17759,7 @@
         <f t="shared" si="4"/>
         <v>29.4</v>
       </c>
-      <c r="S31" s="45"/>
+      <c r="S31" s="44"/>
       <c r="T31" s="23">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -17919,7 +17918,7 @@
         <f t="shared" si="4"/>
         <v>73.7684</v>
       </c>
-      <c r="S32" s="45">
+      <c r="S32" s="44">
         <v>340</v>
       </c>
       <c r="T32" s="23">
@@ -18078,7 +18077,7 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S33" s="45"/>
+      <c r="S33" s="44"/>
       <c r="T33" s="23">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -18240,7 +18239,7 @@
         <f t="shared" si="4"/>
         <v>9.1999999999999993</v>
       </c>
-      <c r="S34" s="45">
+      <c r="S34" s="44">
         <v>80</v>
       </c>
       <c r="T34" s="23">
@@ -18401,7 +18400,7 @@
         <f t="shared" si="4"/>
         <v>131.6</v>
       </c>
-      <c r="S35" s="45"/>
+      <c r="S35" s="44"/>
       <c r="T35" s="23">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -18560,7 +18559,7 @@
         <f t="shared" si="4"/>
         <v>111</v>
       </c>
-      <c r="S36" s="45"/>
+      <c r="S36" s="44"/>
       <c r="T36" s="23">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -18722,7 +18721,7 @@
         <f t="shared" si="4"/>
         <v>162.6</v>
       </c>
-      <c r="S37" s="45"/>
+      <c r="S37" s="44"/>
       <c r="T37" s="23">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -18881,7 +18880,7 @@
         <f t="shared" si="4"/>
         <v>72.400000000000006</v>
       </c>
-      <c r="S38" s="45">
+      <c r="S38" s="44">
         <v>240</v>
       </c>
       <c r="T38" s="23">
@@ -19042,7 +19041,7 @@
         <f t="shared" si="4"/>
         <v>44</v>
       </c>
-      <c r="S39" s="45"/>
+      <c r="S39" s="44"/>
       <c r="T39" s="23">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -19201,7 +19200,7 @@
         <f t="shared" si="4"/>
         <v>25.2</v>
       </c>
-      <c r="S40" s="45">
+      <c r="S40" s="44">
         <v>160</v>
       </c>
       <c r="T40" s="23">
@@ -19362,7 +19361,7 @@
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="S41" s="45"/>
+      <c r="S41" s="44"/>
       <c r="T41" s="23">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -19521,7 +19520,7 @@
         <f t="shared" si="4"/>
         <v>42</v>
       </c>
-      <c r="S42" s="45">
+      <c r="S42" s="44">
         <v>420</v>
       </c>
       <c r="T42" s="23">
@@ -19682,7 +19681,7 @@
         <f t="shared" si="4"/>
         <v>22.845599999999997</v>
       </c>
-      <c r="S43" s="45">
+      <c r="S43" s="44">
         <v>100</v>
       </c>
       <c r="T43" s="23">
@@ -19843,7 +19842,7 @@
         <f t="shared" si="4"/>
         <v>14.439599999999999</v>
       </c>
-      <c r="S44" s="45">
+      <c r="S44" s="44">
         <v>80</v>
       </c>
       <c r="T44" s="23">
@@ -20004,7 +20003,7 @@
         <f t="shared" si="4"/>
         <v>24.6816</v>
       </c>
-      <c r="S45" s="45">
+      <c r="S45" s="44">
         <v>100</v>
       </c>
       <c r="T45" s="23">
@@ -20165,7 +20164,7 @@
         <f t="shared" si="4"/>
         <v>42.509799999999998</v>
       </c>
-      <c r="S46" s="45">
+      <c r="S46" s="44">
         <v>220</v>
       </c>
       <c r="T46" s="23">
@@ -20326,7 +20325,7 @@
         <f t="shared" si="4"/>
         <v>1125</v>
       </c>
-      <c r="S47" s="45">
+      <c r="S47" s="44">
         <v>1700</v>
       </c>
       <c r="T47" s="23">
@@ -20490,7 +20489,7 @@
         <f t="shared" si="4"/>
         <v>2.6646000000000001</v>
       </c>
-      <c r="S48" s="45"/>
+      <c r="S48" s="44"/>
       <c r="T48" s="23">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -20649,7 +20648,7 @@
         <f t="shared" si="4"/>
         <v>254.4</v>
       </c>
-      <c r="S49" s="45">
+      <c r="S49" s="44">
         <v>1800</v>
       </c>
       <c r="T49" s="23">
@@ -20810,7 +20809,7 @@
         <f t="shared" si="4"/>
         <v>90</v>
       </c>
-      <c r="S50" s="45">
+      <c r="S50" s="44">
         <v>160</v>
       </c>
       <c r="T50" s="23">
@@ -20971,7 +20970,7 @@
         <f t="shared" si="4"/>
         <v>24.6</v>
       </c>
-      <c r="S51" s="45">
+      <c r="S51" s="44">
         <v>160</v>
       </c>
       <c r="T51" s="23">
@@ -21132,7 +21131,7 @@
         <f t="shared" si="4"/>
         <v>61.8</v>
       </c>
-      <c r="S52" s="45">
+      <c r="S52" s="44">
         <v>320</v>
       </c>
       <c r="T52" s="23">
@@ -21293,7 +21292,7 @@
         <f t="shared" si="4"/>
         <v>54.2</v>
       </c>
-      <c r="S53" s="45">
+      <c r="S53" s="44">
         <v>140</v>
       </c>
       <c r="T53" s="23">
@@ -21452,7 +21451,7 @@
         <f t="shared" si="4"/>
         <v>-0.2</v>
       </c>
-      <c r="S54" s="45"/>
+      <c r="S54" s="44"/>
       <c r="T54" s="23">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -21611,7 +21610,7 @@
         <f t="shared" si="4"/>
         <v>37.4</v>
       </c>
-      <c r="S55" s="45">
+      <c r="S55" s="44">
         <v>80</v>
       </c>
       <c r="T55" s="23">
@@ -21772,7 +21771,7 @@
         <f t="shared" si="4"/>
         <v>6.2</v>
       </c>
-      <c r="S56" s="45"/>
+      <c r="S56" s="44"/>
       <c r="T56" s="23">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -21931,7 +21930,7 @@
         <f t="shared" si="4"/>
         <v>93.295600000000007</v>
       </c>
-      <c r="S57" s="45">
+      <c r="S57" s="44">
         <v>520</v>
       </c>
       <c r="T57" s="23">
@@ -22090,7 +22089,7 @@
         <f t="shared" si="4"/>
         <v>8.5906000000000002</v>
       </c>
-      <c r="S58" s="45">
+      <c r="S58" s="44">
         <v>100</v>
       </c>
       <c r="T58" s="23">
@@ -22249,7 +22248,7 @@
         <f t="shared" si="4"/>
         <v>2.8</v>
       </c>
-      <c r="S59" s="45"/>
+      <c r="S59" s="44"/>
       <c r="T59" s="23">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -22408,7 +22407,7 @@
         <f t="shared" si="4"/>
         <v>9</v>
       </c>
-      <c r="S60" s="45">
+      <c r="S60" s="44">
         <v>100</v>
       </c>
       <c r="T60" s="23">
@@ -22569,7 +22568,7 @@
         <f t="shared" si="4"/>
         <v>0.76580000000000004</v>
       </c>
-      <c r="S61" s="45"/>
+      <c r="S61" s="44"/>
       <c r="T61" s="23">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -22728,7 +22727,7 @@
         <f t="shared" si="4"/>
         <v>4.5280000000000005</v>
       </c>
-      <c r="S62" s="45">
+      <c r="S62" s="44">
         <v>50</v>
       </c>
       <c r="T62" s="23">
@@ -22887,7 +22886,7 @@
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="S63" s="45"/>
+      <c r="S63" s="44"/>
       <c r="T63" s="23">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -23046,7 +23045,7 @@
         <f t="shared" si="4"/>
         <v>4.5999999999999996</v>
       </c>
-      <c r="S64" s="45"/>
+      <c r="S64" s="44"/>
       <c r="T64" s="23">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -23205,7 +23204,7 @@
         <f t="shared" si="4"/>
         <v>3.4206000000000003</v>
       </c>
-      <c r="S65" s="45">
+      <c r="S65" s="44">
         <v>20</v>
       </c>
       <c r="T65" s="23">
@@ -23366,7 +23365,7 @@
         <f t="shared" si="4"/>
         <v>26.2</v>
       </c>
-      <c r="S66" s="45">
+      <c r="S66" s="44">
         <v>170</v>
       </c>
       <c r="T66" s="23">
@@ -23527,7 +23526,7 @@
         <f t="shared" si="4"/>
         <v>282</v>
       </c>
-      <c r="S67" s="45">
+      <c r="S67" s="44">
         <v>400</v>
       </c>
       <c r="T67" s="23">
@@ -23687,7 +23686,7 @@
         <f t="shared" si="4"/>
         <v>94.911000000000001</v>
       </c>
-      <c r="S68" s="45">
+      <c r="S68" s="44">
         <v>600</v>
       </c>
       <c r="T68" s="23">
@@ -23848,7 +23847,7 @@
         <f t="shared" si="4"/>
         <v>9.4</v>
       </c>
-      <c r="S69" s="45">
+      <c r="S69" s="44">
         <v>50</v>
       </c>
       <c r="T69" s="23">
@@ -24012,7 +24011,7 @@
         <f t="shared" si="4"/>
         <v>124</v>
       </c>
-      <c r="S70" s="45"/>
+      <c r="S70" s="44"/>
       <c r="T70" s="23">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -24171,7 +24170,7 @@
         <f t="shared" si="4"/>
         <v>39</v>
       </c>
-      <c r="S71" s="45">
+      <c r="S71" s="44">
         <v>120</v>
       </c>
       <c r="T71" s="23">
@@ -24333,7 +24332,7 @@
         <f t="shared" si="4"/>
         <v>-0.6</v>
       </c>
-      <c r="S72" s="45"/>
+      <c r="S72" s="44"/>
       <c r="T72" s="23">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -24492,7 +24491,7 @@
         <f t="shared" si="4"/>
         <v>48.6</v>
       </c>
-      <c r="S73" s="45"/>
+      <c r="S73" s="44"/>
       <c r="T73" s="23">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -24648,7 +24647,7 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S74" s="45"/>
+      <c r="S74" s="44"/>
       <c r="T74" s="23">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -24807,7 +24806,7 @@
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="S75" s="45">
+      <c r="S75" s="44">
         <v>24</v>
       </c>
       <c r="T75" s="23">
@@ -24971,7 +24970,7 @@
         <f t="shared" ref="R76:R100" si="12">F76/5</f>
         <v>176.6688</v>
       </c>
-      <c r="S76" s="45">
+      <c r="S76" s="44">
         <v>1200</v>
       </c>
       <c r="T76" s="23">
@@ -25132,7 +25131,7 @@
         <f t="shared" si="12"/>
         <v>24.487000000000002</v>
       </c>
-      <c r="S77" s="45">
+      <c r="S77" s="44">
         <v>120</v>
       </c>
       <c r="T77" s="23">
@@ -25291,7 +25290,7 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="S78" s="45"/>
+      <c r="S78" s="44"/>
       <c r="T78" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
@@ -25450,7 +25449,7 @@
         <f t="shared" si="12"/>
         <v>77.6614</v>
       </c>
-      <c r="S79" s="45">
+      <c r="S79" s="44">
         <v>220</v>
       </c>
       <c r="T79" s="23">
@@ -25611,7 +25610,7 @@
         <f t="shared" si="12"/>
         <v>173.4</v>
       </c>
-      <c r="S80" s="45">
+      <c r="S80" s="44">
         <v>800</v>
       </c>
       <c r="T80" s="23">
@@ -25772,7 +25771,7 @@
         <f t="shared" si="12"/>
         <v>22</v>
       </c>
-      <c r="S81" s="45">
+      <c r="S81" s="44">
         <v>160</v>
       </c>
       <c r="T81" s="23">
@@ -25931,7 +25930,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="S82" s="45"/>
+      <c r="S82" s="44"/>
       <c r="T82" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
@@ -26088,7 +26087,7 @@
         <f t="shared" si="12"/>
         <v>15</v>
       </c>
-      <c r="S83" s="45">
+      <c r="S83" s="44">
         <v>100</v>
       </c>
       <c r="T83" s="23">
@@ -26249,7 +26248,7 @@
         <f t="shared" si="12"/>
         <v>32.6</v>
       </c>
-      <c r="S84" s="45"/>
+      <c r="S84" s="44"/>
       <c r="T84" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
@@ -26408,7 +26407,7 @@
         <f t="shared" si="12"/>
         <v>60.4</v>
       </c>
-      <c r="S85" s="45">
+      <c r="S85" s="44">
         <v>660</v>
       </c>
       <c r="T85" s="23">
@@ -26569,7 +26568,7 @@
         <f t="shared" si="12"/>
         <v>10.8</v>
       </c>
-      <c r="S86" s="45"/>
+      <c r="S86" s="44"/>
       <c r="T86" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
@@ -26728,7 +26727,7 @@
         <f t="shared" si="12"/>
         <v>51</v>
       </c>
-      <c r="S87" s="45">
+      <c r="S87" s="44">
         <v>300</v>
       </c>
       <c r="T87" s="23">
@@ -26889,7 +26888,7 @@
         <f t="shared" si="12"/>
         <v>89.6</v>
       </c>
-      <c r="S88" s="45">
+      <c r="S88" s="44">
         <v>840</v>
       </c>
       <c r="T88" s="23">
@@ -27050,7 +27049,7 @@
         <f t="shared" si="12"/>
         <v>2.4</v>
       </c>
-      <c r="S89" s="45"/>
+      <c r="S89" s="44"/>
       <c r="T89" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
@@ -27209,7 +27208,7 @@
         <f t="shared" si="12"/>
         <v>3.6</v>
       </c>
-      <c r="S90" s="45"/>
+      <c r="S90" s="44"/>
       <c r="T90" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
@@ -27368,7 +27367,7 @@
         <f t="shared" si="12"/>
         <v>13</v>
       </c>
-      <c r="S91" s="45">
+      <c r="S91" s="44">
         <v>140</v>
       </c>
       <c r="T91" s="23">
@@ -27529,7 +27528,7 @@
         <f t="shared" si="12"/>
         <v>4.4000000000000004</v>
       </c>
-      <c r="S92" s="45"/>
+      <c r="S92" s="44"/>
       <c r="T92" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
@@ -27691,7 +27690,7 @@
         <f t="shared" si="12"/>
         <v>4</v>
       </c>
-      <c r="S93" s="45"/>
+      <c r="S93" s="44"/>
       <c r="T93" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
@@ -27850,7 +27849,7 @@
         <f t="shared" si="12"/>
         <v>32.6</v>
       </c>
-      <c r="S94" s="45">
+      <c r="S94" s="44">
         <v>180</v>
       </c>
       <c r="T94" s="23">
@@ -28011,7 +28010,7 @@
         <f t="shared" si="12"/>
         <v>50.6</v>
       </c>
-      <c r="S95" s="45">
+      <c r="S95" s="44">
         <v>280</v>
       </c>
       <c r="T95" s="23">
@@ -28172,7 +28171,7 @@
         <f t="shared" si="12"/>
         <v>56.2</v>
       </c>
-      <c r="S96" s="45">
+      <c r="S96" s="44">
         <v>400</v>
       </c>
       <c r="T96" s="23">
@@ -28333,7 +28332,7 @@
         <f t="shared" si="12"/>
         <v>35.200000000000003</v>
       </c>
-      <c r="S97" s="45">
+      <c r="S97" s="44">
         <v>400</v>
       </c>
       <c r="T97" s="23">
@@ -28494,7 +28493,7 @@
         <f t="shared" si="12"/>
         <v>4.6631999999999998</v>
       </c>
-      <c r="S98" s="45"/>
+      <c r="S98" s="44"/>
       <c r="T98" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
@@ -28651,7 +28650,7 @@
         <f t="shared" si="12"/>
         <v>2.6</v>
       </c>
-      <c r="S99" s="45"/>
+      <c r="S99" s="44"/>
       <c r="T99" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
@@ -28809,7 +28808,7 @@
         <f t="shared" si="12"/>
         <v>12.635999999999999</v>
       </c>
-      <c r="S100" s="45"/>
+      <c r="S100" s="44"/>
       <c r="T100" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
@@ -28927,7 +28926,7 @@
       <c r="P101" s="9"/>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
-      <c r="S101" s="45"/>
+      <c r="S101" s="44"/>
       <c r="T101" s="36"/>
       <c r="U101" s="36"/>
       <c r="V101" s="9"/>
@@ -29009,7 +29008,7 @@
       <c r="P102" s="9"/>
       <c r="Q102" s="9"/>
       <c r="R102" s="9"/>
-      <c r="S102" s="46"/>
+      <c r="S102" s="45"/>
       <c r="T102" s="36"/>
       <c r="U102" s="36"/>
       <c r="V102" s="9"/>
@@ -29091,7 +29090,7 @@
       <c r="P103" s="9"/>
       <c r="Q103" s="9"/>
       <c r="R103" s="9"/>
-      <c r="S103" s="46"/>
+      <c r="S103" s="45"/>
       <c r="T103" s="36"/>
       <c r="U103" s="36"/>
       <c r="V103" s="9"/>
@@ -29173,7 +29172,7 @@
       <c r="P104" s="9"/>
       <c r="Q104" s="9"/>
       <c r="R104" s="9"/>
-      <c r="S104" s="46"/>
+      <c r="S104" s="45"/>
       <c r="T104" s="36"/>
       <c r="U104" s="36"/>
       <c r="V104" s="9"/>
@@ -29255,7 +29254,7 @@
       <c r="P105" s="9"/>
       <c r="Q105" s="9"/>
       <c r="R105" s="9"/>
-      <c r="S105" s="46"/>
+      <c r="S105" s="45"/>
       <c r="T105" s="36"/>
       <c r="U105" s="36"/>
       <c r="V105" s="9"/>
@@ -29337,7 +29336,7 @@
       <c r="P106" s="9"/>
       <c r="Q106" s="9"/>
       <c r="R106" s="9"/>
-      <c r="S106" s="46"/>
+      <c r="S106" s="45"/>
       <c r="T106" s="36"/>
       <c r="U106" s="36"/>
       <c r="V106" s="9"/>
@@ -29419,7 +29418,7 @@
       <c r="P107" s="9"/>
       <c r="Q107" s="9"/>
       <c r="R107" s="9"/>
-      <c r="S107" s="46"/>
+      <c r="S107" s="45"/>
       <c r="T107" s="36"/>
       <c r="U107" s="36"/>
       <c r="V107" s="9"/>
@@ -29501,7 +29500,7 @@
       <c r="P108" s="9"/>
       <c r="Q108" s="9"/>
       <c r="R108" s="9"/>
-      <c r="S108" s="46"/>
+      <c r="S108" s="45"/>
       <c r="T108" s="36"/>
       <c r="U108" s="36"/>
       <c r="V108" s="9"/>
@@ -29583,7 +29582,7 @@
       <c r="P109" s="9"/>
       <c r="Q109" s="9"/>
       <c r="R109" s="9"/>
-      <c r="S109" s="46"/>
+      <c r="S109" s="45"/>
       <c r="T109" s="36"/>
       <c r="U109" s="36"/>
       <c r="V109" s="9"/>
@@ -29665,7 +29664,7 @@
       <c r="P110" s="9"/>
       <c r="Q110" s="9"/>
       <c r="R110" s="9"/>
-      <c r="S110" s="46"/>
+      <c r="S110" s="45"/>
       <c r="T110" s="36"/>
       <c r="U110" s="36"/>
       <c r="V110" s="9"/>
@@ -29747,7 +29746,7 @@
       <c r="P111" s="9"/>
       <c r="Q111" s="9"/>
       <c r="R111" s="9"/>
-      <c r="S111" s="46"/>
+      <c r="S111" s="45"/>
       <c r="T111" s="36"/>
       <c r="U111" s="36"/>
       <c r="V111" s="9"/>
@@ -29829,7 +29828,7 @@
       <c r="P112" s="9"/>
       <c r="Q112" s="9"/>
       <c r="R112" s="9"/>
-      <c r="S112" s="46"/>
+      <c r="S112" s="45"/>
       <c r="T112" s="36"/>
       <c r="U112" s="36"/>
       <c r="V112" s="9"/>
@@ -29911,7 +29910,7 @@
       <c r="P113" s="9"/>
       <c r="Q113" s="9"/>
       <c r="R113" s="9"/>
-      <c r="S113" s="46"/>
+      <c r="S113" s="45"/>
       <c r="T113" s="36"/>
       <c r="U113" s="36"/>
       <c r="V113" s="9"/>
@@ -29993,7 +29992,7 @@
       <c r="P114" s="9"/>
       <c r="Q114" s="9"/>
       <c r="R114" s="9"/>
-      <c r="S114" s="46"/>
+      <c r="S114" s="45"/>
       <c r="T114" s="36"/>
       <c r="U114" s="36"/>
       <c r="V114" s="9"/>
@@ -30075,7 +30074,7 @@
       <c r="P115" s="9"/>
       <c r="Q115" s="9"/>
       <c r="R115" s="9"/>
-      <c r="S115" s="46"/>
+      <c r="S115" s="45"/>
       <c r="T115" s="36"/>
       <c r="U115" s="36"/>
       <c r="V115" s="9"/>
@@ -30157,7 +30156,7 @@
       <c r="P116" s="9"/>
       <c r="Q116" s="9"/>
       <c r="R116" s="9"/>
-      <c r="S116" s="46"/>
+      <c r="S116" s="45"/>
       <c r="T116" s="36"/>
       <c r="U116" s="36"/>
       <c r="V116" s="9"/>
@@ -30239,7 +30238,7 @@
       <c r="P117" s="9"/>
       <c r="Q117" s="9"/>
       <c r="R117" s="9"/>
-      <c r="S117" s="46"/>
+      <c r="S117" s="45"/>
       <c r="T117" s="36"/>
       <c r="U117" s="36"/>
       <c r="V117" s="9"/>
@@ -30321,7 +30320,7 @@
       <c r="P118" s="9"/>
       <c r="Q118" s="9"/>
       <c r="R118" s="9"/>
-      <c r="S118" s="46"/>
+      <c r="S118" s="45"/>
       <c r="T118" s="36"/>
       <c r="U118" s="36"/>
       <c r="V118" s="9"/>
@@ -30403,7 +30402,7 @@
       <c r="P119" s="9"/>
       <c r="Q119" s="9"/>
       <c r="R119" s="9"/>
-      <c r="S119" s="46"/>
+      <c r="S119" s="45"/>
       <c r="T119" s="36"/>
       <c r="U119" s="36"/>
       <c r="V119" s="9"/>
@@ -30485,7 +30484,7 @@
       <c r="P120" s="9"/>
       <c r="Q120" s="9"/>
       <c r="R120" s="9"/>
-      <c r="S120" s="46"/>
+      <c r="S120" s="45"/>
       <c r="T120" s="36"/>
       <c r="U120" s="36"/>
       <c r="V120" s="9"/>
@@ -30567,7 +30566,7 @@
       <c r="P121" s="9"/>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
-      <c r="S121" s="46"/>
+      <c r="S121" s="45"/>
       <c r="T121" s="36"/>
       <c r="U121" s="36"/>
       <c r="V121" s="9"/>
@@ -30649,7 +30648,7 @@
       <c r="P122" s="9"/>
       <c r="Q122" s="9"/>
       <c r="R122" s="9"/>
-      <c r="S122" s="46"/>
+      <c r="S122" s="45"/>
       <c r="T122" s="36"/>
       <c r="U122" s="36"/>
       <c r="V122" s="9"/>
@@ -30731,7 +30730,7 @@
       <c r="P123" s="9"/>
       <c r="Q123" s="9"/>
       <c r="R123" s="9"/>
-      <c r="S123" s="46"/>
+      <c r="S123" s="45"/>
       <c r="T123" s="36"/>
       <c r="U123" s="36"/>
       <c r="V123" s="9"/>
@@ -30813,7 +30812,7 @@
       <c r="P124" s="9"/>
       <c r="Q124" s="9"/>
       <c r="R124" s="9"/>
-      <c r="S124" s="46"/>
+      <c r="S124" s="45"/>
       <c r="T124" s="36"/>
       <c r="U124" s="36"/>
       <c r="V124" s="9"/>
@@ -30895,7 +30894,7 @@
       <c r="P125" s="9"/>
       <c r="Q125" s="9"/>
       <c r="R125" s="9"/>
-      <c r="S125" s="46"/>
+      <c r="S125" s="45"/>
       <c r="T125" s="36"/>
       <c r="U125" s="36"/>
       <c r="V125" s="9"/>
@@ -30977,7 +30976,7 @@
       <c r="P126" s="9"/>
       <c r="Q126" s="9"/>
       <c r="R126" s="9"/>
-      <c r="S126" s="46"/>
+      <c r="S126" s="45"/>
       <c r="T126" s="36"/>
       <c r="U126" s="36"/>
       <c r="V126" s="9"/>
@@ -31059,7 +31058,7 @@
       <c r="P127" s="9"/>
       <c r="Q127" s="9"/>
       <c r="R127" s="9"/>
-      <c r="S127" s="46"/>
+      <c r="S127" s="45"/>
       <c r="T127" s="36"/>
       <c r="U127" s="36"/>
       <c r="V127" s="9"/>
@@ -31141,7 +31140,7 @@
       <c r="P128" s="9"/>
       <c r="Q128" s="9"/>
       <c r="R128" s="9"/>
-      <c r="S128" s="46"/>
+      <c r="S128" s="45"/>
       <c r="T128" s="36"/>
       <c r="U128" s="36"/>
       <c r="V128" s="9"/>
@@ -31223,7 +31222,7 @@
       <c r="P129" s="9"/>
       <c r="Q129" s="9"/>
       <c r="R129" s="9"/>
-      <c r="S129" s="46"/>
+      <c r="S129" s="45"/>
       <c r="T129" s="36"/>
       <c r="U129" s="36"/>
       <c r="V129" s="9"/>
@@ -31305,7 +31304,7 @@
       <c r="P130" s="9"/>
       <c r="Q130" s="9"/>
       <c r="R130" s="9"/>
-      <c r="S130" s="46"/>
+      <c r="S130" s="45"/>
       <c r="T130" s="36"/>
       <c r="U130" s="36"/>
       <c r="V130" s="9"/>
@@ -31387,7 +31386,7 @@
       <c r="P131" s="9"/>
       <c r="Q131" s="9"/>
       <c r="R131" s="9"/>
-      <c r="S131" s="46"/>
+      <c r="S131" s="45"/>
       <c r="T131" s="36"/>
       <c r="U131" s="36"/>
       <c r="V131" s="9"/>
@@ -31469,7 +31468,7 @@
       <c r="P132" s="9"/>
       <c r="Q132" s="9"/>
       <c r="R132" s="9"/>
-      <c r="S132" s="46"/>
+      <c r="S132" s="45"/>
       <c r="T132" s="36"/>
       <c r="U132" s="36"/>
       <c r="V132" s="9"/>
@@ -31551,7 +31550,7 @@
       <c r="P133" s="9"/>
       <c r="Q133" s="9"/>
       <c r="R133" s="9"/>
-      <c r="S133" s="46"/>
+      <c r="S133" s="45"/>
       <c r="T133" s="36"/>
       <c r="U133" s="36"/>
       <c r="V133" s="9"/>
@@ -31633,7 +31632,7 @@
       <c r="P134" s="9"/>
       <c r="Q134" s="9"/>
       <c r="R134" s="9"/>
-      <c r="S134" s="46"/>
+      <c r="S134" s="45"/>
       <c r="T134" s="36"/>
       <c r="U134" s="36"/>
       <c r="V134" s="9"/>
@@ -31715,7 +31714,7 @@
       <c r="P135" s="9"/>
       <c r="Q135" s="9"/>
       <c r="R135" s="9"/>
-      <c r="S135" s="46"/>
+      <c r="S135" s="45"/>
       <c r="T135" s="36"/>
       <c r="U135" s="36"/>
       <c r="V135" s="9"/>
@@ -31797,7 +31796,7 @@
       <c r="P136" s="9"/>
       <c r="Q136" s="9"/>
       <c r="R136" s="9"/>
-      <c r="S136" s="46"/>
+      <c r="S136" s="45"/>
       <c r="T136" s="36"/>
       <c r="U136" s="36"/>
       <c r="V136" s="9"/>
@@ -31879,7 +31878,7 @@
       <c r="P137" s="9"/>
       <c r="Q137" s="9"/>
       <c r="R137" s="9"/>
-      <c r="S137" s="46"/>
+      <c r="S137" s="45"/>
       <c r="T137" s="36"/>
       <c r="U137" s="36"/>
       <c r="V137" s="9"/>
@@ -31961,7 +31960,7 @@
       <c r="P138" s="9"/>
       <c r="Q138" s="9"/>
       <c r="R138" s="9"/>
-      <c r="S138" s="46"/>
+      <c r="S138" s="45"/>
       <c r="T138" s="36"/>
       <c r="U138" s="36"/>
       <c r="V138" s="9"/>
@@ -32043,7 +32042,7 @@
       <c r="P139" s="9"/>
       <c r="Q139" s="9"/>
       <c r="R139" s="9"/>
-      <c r="S139" s="46"/>
+      <c r="S139" s="45"/>
       <c r="T139" s="36"/>
       <c r="U139" s="36"/>
       <c r="V139" s="9"/>
@@ -32125,7 +32124,7 @@
       <c r="P140" s="9"/>
       <c r="Q140" s="9"/>
       <c r="R140" s="9"/>
-      <c r="S140" s="46"/>
+      <c r="S140" s="45"/>
       <c r="T140" s="36"/>
       <c r="U140" s="36"/>
       <c r="V140" s="9"/>
@@ -32207,7 +32206,7 @@
       <c r="P141" s="9"/>
       <c r="Q141" s="9"/>
       <c r="R141" s="9"/>
-      <c r="S141" s="46"/>
+      <c r="S141" s="45"/>
       <c r="T141" s="36"/>
       <c r="U141" s="36"/>
       <c r="V141" s="9"/>
@@ -32289,7 +32288,7 @@
       <c r="P142" s="9"/>
       <c r="Q142" s="9"/>
       <c r="R142" s="9"/>
-      <c r="S142" s="46"/>
+      <c r="S142" s="45"/>
       <c r="T142" s="36"/>
       <c r="U142" s="36"/>
       <c r="V142" s="9"/>
@@ -32371,7 +32370,7 @@
       <c r="P143" s="9"/>
       <c r="Q143" s="9"/>
       <c r="R143" s="9"/>
-      <c r="S143" s="46"/>
+      <c r="S143" s="45"/>
       <c r="T143" s="36"/>
       <c r="U143" s="36"/>
       <c r="V143" s="9"/>
@@ -32453,7 +32452,7 @@
       <c r="P144" s="9"/>
       <c r="Q144" s="9"/>
       <c r="R144" s="9"/>
-      <c r="S144" s="46"/>
+      <c r="S144" s="45"/>
       <c r="T144" s="36"/>
       <c r="U144" s="36"/>
       <c r="V144" s="9"/>
@@ -32535,7 +32534,7 @@
       <c r="P145" s="9"/>
       <c r="Q145" s="9"/>
       <c r="R145" s="9"/>
-      <c r="S145" s="46"/>
+      <c r="S145" s="45"/>
       <c r="T145" s="36"/>
       <c r="U145" s="36"/>
       <c r="V145" s="9"/>
@@ -32617,7 +32616,7 @@
       <c r="P146" s="9"/>
       <c r="Q146" s="9"/>
       <c r="R146" s="9"/>
-      <c r="S146" s="46"/>
+      <c r="S146" s="45"/>
       <c r="T146" s="36"/>
       <c r="U146" s="36"/>
       <c r="V146" s="9"/>
@@ -32699,7 +32698,7 @@
       <c r="P147" s="9"/>
       <c r="Q147" s="9"/>
       <c r="R147" s="9"/>
-      <c r="S147" s="46"/>
+      <c r="S147" s="45"/>
       <c r="T147" s="36"/>
       <c r="U147" s="36"/>
       <c r="V147" s="9"/>
@@ -32781,7 +32780,7 @@
       <c r="P148" s="9"/>
       <c r="Q148" s="9"/>
       <c r="R148" s="9"/>
-      <c r="S148" s="46"/>
+      <c r="S148" s="45"/>
       <c r="T148" s="36"/>
       <c r="U148" s="36"/>
       <c r="V148" s="9"/>
@@ -32863,7 +32862,7 @@
       <c r="P149" s="9"/>
       <c r="Q149" s="9"/>
       <c r="R149" s="9"/>
-      <c r="S149" s="46"/>
+      <c r="S149" s="45"/>
       <c r="T149" s="36"/>
       <c r="U149" s="36"/>
       <c r="V149" s="9"/>
@@ -32945,7 +32944,7 @@
       <c r="P150" s="9"/>
       <c r="Q150" s="9"/>
       <c r="R150" s="9"/>
-      <c r="S150" s="46"/>
+      <c r="S150" s="45"/>
       <c r="T150" s="36"/>
       <c r="U150" s="36"/>
       <c r="V150" s="9"/>
@@ -33027,7 +33026,7 @@
       <c r="P151" s="9"/>
       <c r="Q151" s="9"/>
       <c r="R151" s="9"/>
-      <c r="S151" s="46"/>
+      <c r="S151" s="45"/>
       <c r="T151" s="36"/>
       <c r="U151" s="36"/>
       <c r="V151" s="9"/>
@@ -33109,7 +33108,7 @@
       <c r="P152" s="9"/>
       <c r="Q152" s="9"/>
       <c r="R152" s="9"/>
-      <c r="S152" s="46"/>
+      <c r="S152" s="45"/>
       <c r="T152" s="36"/>
       <c r="U152" s="36"/>
       <c r="V152" s="9"/>
@@ -33191,7 +33190,7 @@
       <c r="P153" s="9"/>
       <c r="Q153" s="9"/>
       <c r="R153" s="9"/>
-      <c r="S153" s="46"/>
+      <c r="S153" s="45"/>
       <c r="T153" s="36"/>
       <c r="U153" s="36"/>
       <c r="V153" s="9"/>
@@ -33273,7 +33272,7 @@
       <c r="P154" s="9"/>
       <c r="Q154" s="9"/>
       <c r="R154" s="9"/>
-      <c r="S154" s="46"/>
+      <c r="S154" s="45"/>
       <c r="T154" s="36"/>
       <c r="U154" s="36"/>
       <c r="V154" s="9"/>
@@ -33355,7 +33354,7 @@
       <c r="P155" s="9"/>
       <c r="Q155" s="9"/>
       <c r="R155" s="9"/>
-      <c r="S155" s="46"/>
+      <c r="S155" s="45"/>
       <c r="T155" s="36"/>
       <c r="U155" s="36"/>
       <c r="V155" s="9"/>
@@ -33437,7 +33436,7 @@
       <c r="P156" s="9"/>
       <c r="Q156" s="9"/>
       <c r="R156" s="9"/>
-      <c r="S156" s="46"/>
+      <c r="S156" s="45"/>
       <c r="T156" s="36"/>
       <c r="U156" s="36"/>
       <c r="V156" s="9"/>
@@ -33519,7 +33518,7 @@
       <c r="P157" s="9"/>
       <c r="Q157" s="9"/>
       <c r="R157" s="9"/>
-      <c r="S157" s="46"/>
+      <c r="S157" s="45"/>
       <c r="T157" s="36"/>
       <c r="U157" s="36"/>
       <c r="V157" s="9"/>
@@ -33601,7 +33600,7 @@
       <c r="P158" s="9"/>
       <c r="Q158" s="9"/>
       <c r="R158" s="9"/>
-      <c r="S158" s="46"/>
+      <c r="S158" s="45"/>
       <c r="T158" s="36"/>
       <c r="U158" s="36"/>
       <c r="V158" s="9"/>
@@ -33683,7 +33682,7 @@
       <c r="P159" s="9"/>
       <c r="Q159" s="9"/>
       <c r="R159" s="9"/>
-      <c r="S159" s="46"/>
+      <c r="S159" s="45"/>
       <c r="T159" s="36"/>
       <c r="U159" s="36"/>
       <c r="V159" s="9"/>
@@ -33765,7 +33764,7 @@
       <c r="P160" s="9"/>
       <c r="Q160" s="9"/>
       <c r="R160" s="9"/>
-      <c r="S160" s="46"/>
+      <c r="S160" s="45"/>
       <c r="T160" s="36"/>
       <c r="U160" s="36"/>
       <c r="V160" s="9"/>
@@ -33847,7 +33846,7 @@
       <c r="P161" s="9"/>
       <c r="Q161" s="9"/>
       <c r="R161" s="9"/>
-      <c r="S161" s="46"/>
+      <c r="S161" s="45"/>
       <c r="T161" s="36"/>
       <c r="U161" s="36"/>
       <c r="V161" s="9"/>
@@ -33929,7 +33928,7 @@
       <c r="P162" s="9"/>
       <c r="Q162" s="9"/>
       <c r="R162" s="9"/>
-      <c r="S162" s="46"/>
+      <c r="S162" s="45"/>
       <c r="T162" s="36"/>
       <c r="U162" s="36"/>
       <c r="V162" s="9"/>
@@ -34011,7 +34010,7 @@
       <c r="P163" s="9"/>
       <c r="Q163" s="9"/>
       <c r="R163" s="9"/>
-      <c r="S163" s="46"/>
+      <c r="S163" s="45"/>
       <c r="T163" s="36"/>
       <c r="U163" s="36"/>
       <c r="V163" s="9"/>
@@ -34093,7 +34092,7 @@
       <c r="P164" s="9"/>
       <c r="Q164" s="9"/>
       <c r="R164" s="9"/>
-      <c r="S164" s="46"/>
+      <c r="S164" s="45"/>
       <c r="T164" s="36"/>
       <c r="U164" s="36"/>
       <c r="V164" s="9"/>
@@ -34175,7 +34174,7 @@
       <c r="P165" s="9"/>
       <c r="Q165" s="9"/>
       <c r="R165" s="9"/>
-      <c r="S165" s="46"/>
+      <c r="S165" s="45"/>
       <c r="T165" s="36"/>
       <c r="U165" s="36"/>
       <c r="V165" s="9"/>
@@ -34257,7 +34256,7 @@
       <c r="P166" s="9"/>
       <c r="Q166" s="9"/>
       <c r="R166" s="9"/>
-      <c r="S166" s="46"/>
+      <c r="S166" s="45"/>
       <c r="T166" s="36"/>
       <c r="U166" s="36"/>
       <c r="V166" s="9"/>
@@ -34339,7 +34338,7 @@
       <c r="P167" s="9"/>
       <c r="Q167" s="9"/>
       <c r="R167" s="9"/>
-      <c r="S167" s="46"/>
+      <c r="S167" s="45"/>
       <c r="T167" s="36"/>
       <c r="U167" s="36"/>
       <c r="V167" s="9"/>
@@ -34421,7 +34420,7 @@
       <c r="P168" s="9"/>
       <c r="Q168" s="9"/>
       <c r="R168" s="9"/>
-      <c r="S168" s="46"/>
+      <c r="S168" s="45"/>
       <c r="T168" s="36"/>
       <c r="U168" s="36"/>
       <c r="V168" s="9"/>
@@ -34503,7 +34502,7 @@
       <c r="P169" s="9"/>
       <c r="Q169" s="9"/>
       <c r="R169" s="9"/>
-      <c r="S169" s="46"/>
+      <c r="S169" s="45"/>
       <c r="T169" s="36"/>
       <c r="U169" s="36"/>
       <c r="V169" s="9"/>
@@ -34585,7 +34584,7 @@
       <c r="P170" s="9"/>
       <c r="Q170" s="9"/>
       <c r="R170" s="9"/>
-      <c r="S170" s="46"/>
+      <c r="S170" s="45"/>
       <c r="T170" s="36"/>
       <c r="U170" s="36"/>
       <c r="V170" s="9"/>
@@ -34667,7 +34666,7 @@
       <c r="P171" s="9"/>
       <c r="Q171" s="9"/>
       <c r="R171" s="9"/>
-      <c r="S171" s="46"/>
+      <c r="S171" s="45"/>
       <c r="T171" s="36"/>
       <c r="U171" s="36"/>
       <c r="V171" s="9"/>
@@ -34749,7 +34748,7 @@
       <c r="P172" s="9"/>
       <c r="Q172" s="9"/>
       <c r="R172" s="9"/>
-      <c r="S172" s="46"/>
+      <c r="S172" s="45"/>
       <c r="T172" s="36"/>
       <c r="U172" s="36"/>
       <c r="V172" s="9"/>
@@ -34831,7 +34830,7 @@
       <c r="P173" s="9"/>
       <c r="Q173" s="9"/>
       <c r="R173" s="9"/>
-      <c r="S173" s="46"/>
+      <c r="S173" s="45"/>
       <c r="T173" s="36"/>
       <c r="U173" s="36"/>
       <c r="V173" s="9"/>
@@ -34913,7 +34912,7 @@
       <c r="P174" s="9"/>
       <c r="Q174" s="9"/>
       <c r="R174" s="9"/>
-      <c r="S174" s="46"/>
+      <c r="S174" s="45"/>
       <c r="T174" s="36"/>
       <c r="U174" s="36"/>
       <c r="V174" s="9"/>
@@ -34995,7 +34994,7 @@
       <c r="P175" s="9"/>
       <c r="Q175" s="9"/>
       <c r="R175" s="9"/>
-      <c r="S175" s="46"/>
+      <c r="S175" s="45"/>
       <c r="T175" s="36"/>
       <c r="U175" s="36"/>
       <c r="V175" s="9"/>
@@ -35077,7 +35076,7 @@
       <c r="P176" s="9"/>
       <c r="Q176" s="9"/>
       <c r="R176" s="9"/>
-      <c r="S176" s="46"/>
+      <c r="S176" s="45"/>
       <c r="T176" s="36"/>
       <c r="U176" s="36"/>
       <c r="V176" s="9"/>
@@ -35159,7 +35158,7 @@
       <c r="P177" s="9"/>
       <c r="Q177" s="9"/>
       <c r="R177" s="9"/>
-      <c r="S177" s="46"/>
+      <c r="S177" s="45"/>
       <c r="T177" s="36"/>
       <c r="U177" s="36"/>
       <c r="V177" s="9"/>
@@ -35241,7 +35240,7 @@
       <c r="P178" s="9"/>
       <c r="Q178" s="9"/>
       <c r="R178" s="9"/>
-      <c r="S178" s="46"/>
+      <c r="S178" s="45"/>
       <c r="T178" s="36"/>
       <c r="U178" s="36"/>
       <c r="V178" s="9"/>
@@ -35323,7 +35322,7 @@
       <c r="P179" s="9"/>
       <c r="Q179" s="9"/>
       <c r="R179" s="9"/>
-      <c r="S179" s="46"/>
+      <c r="S179" s="45"/>
       <c r="T179" s="36"/>
       <c r="U179" s="36"/>
       <c r="V179" s="9"/>
@@ -35405,7 +35404,7 @@
       <c r="P180" s="9"/>
       <c r="Q180" s="9"/>
       <c r="R180" s="9"/>
-      <c r="S180" s="46"/>
+      <c r="S180" s="45"/>
       <c r="T180" s="36"/>
       <c r="U180" s="36"/>
       <c r="V180" s="9"/>
@@ -35487,7 +35486,7 @@
       <c r="P181" s="9"/>
       <c r="Q181" s="9"/>
       <c r="R181" s="9"/>
-      <c r="S181" s="46"/>
+      <c r="S181" s="45"/>
       <c r="T181" s="36"/>
       <c r="U181" s="36"/>
       <c r="V181" s="9"/>
@@ -35569,7 +35568,7 @@
       <c r="P182" s="9"/>
       <c r="Q182" s="9"/>
       <c r="R182" s="9"/>
-      <c r="S182" s="46"/>
+      <c r="S182" s="45"/>
       <c r="T182" s="36"/>
       <c r="U182" s="36"/>
       <c r="V182" s="9"/>
@@ -35651,7 +35650,7 @@
       <c r="P183" s="9"/>
       <c r="Q183" s="9"/>
       <c r="R183" s="9"/>
-      <c r="S183" s="46"/>
+      <c r="S183" s="45"/>
       <c r="T183" s="36"/>
       <c r="U183" s="36"/>
       <c r="V183" s="9"/>
@@ -35733,7 +35732,7 @@
       <c r="P184" s="9"/>
       <c r="Q184" s="9"/>
       <c r="R184" s="9"/>
-      <c r="S184" s="46"/>
+      <c r="S184" s="45"/>
       <c r="T184" s="36"/>
       <c r="U184" s="36"/>
       <c r="V184" s="9"/>
@@ -35815,7 +35814,7 @@
       <c r="P185" s="9"/>
       <c r="Q185" s="9"/>
       <c r="R185" s="9"/>
-      <c r="S185" s="46"/>
+      <c r="S185" s="45"/>
       <c r="T185" s="36"/>
       <c r="U185" s="36"/>
       <c r="V185" s="9"/>
@@ -35897,7 +35896,7 @@
       <c r="P186" s="9"/>
       <c r="Q186" s="9"/>
       <c r="R186" s="9"/>
-      <c r="S186" s="46"/>
+      <c r="S186" s="45"/>
       <c r="T186" s="36"/>
       <c r="U186" s="36"/>
       <c r="V186" s="9"/>
@@ -35979,7 +35978,7 @@
       <c r="P187" s="9"/>
       <c r="Q187" s="9"/>
       <c r="R187" s="9"/>
-      <c r="S187" s="46"/>
+      <c r="S187" s="45"/>
       <c r="T187" s="36"/>
       <c r="U187" s="36"/>
       <c r="V187" s="9"/>
@@ -36061,7 +36060,7 @@
       <c r="P188" s="9"/>
       <c r="Q188" s="9"/>
       <c r="R188" s="9"/>
-      <c r="S188" s="46"/>
+      <c r="S188" s="45"/>
       <c r="T188" s="36"/>
       <c r="U188" s="36"/>
       <c r="V188" s="9"/>
@@ -36143,7 +36142,7 @@
       <c r="P189" s="9"/>
       <c r="Q189" s="9"/>
       <c r="R189" s="9"/>
-      <c r="S189" s="46"/>
+      <c r="S189" s="45"/>
       <c r="T189" s="36"/>
       <c r="U189" s="36"/>
       <c r="V189" s="9"/>
@@ -36225,7 +36224,7 @@
       <c r="P190" s="9"/>
       <c r="Q190" s="9"/>
       <c r="R190" s="9"/>
-      <c r="S190" s="46"/>
+      <c r="S190" s="45"/>
       <c r="T190" s="36"/>
       <c r="U190" s="36"/>
       <c r="V190" s="9"/>
@@ -36307,7 +36306,7 @@
       <c r="P191" s="9"/>
       <c r="Q191" s="9"/>
       <c r="R191" s="9"/>
-      <c r="S191" s="46"/>
+      <c r="S191" s="45"/>
       <c r="T191" s="36"/>
       <c r="U191" s="36"/>
       <c r="V191" s="9"/>
@@ -36389,7 +36388,7 @@
       <c r="P192" s="9"/>
       <c r="Q192" s="9"/>
       <c r="R192" s="9"/>
-      <c r="S192" s="46"/>
+      <c r="S192" s="45"/>
       <c r="T192" s="36"/>
       <c r="U192" s="36"/>
       <c r="V192" s="9"/>
@@ -36471,7 +36470,7 @@
       <c r="P193" s="9"/>
       <c r="Q193" s="9"/>
       <c r="R193" s="9"/>
-      <c r="S193" s="46"/>
+      <c r="S193" s="45"/>
       <c r="T193" s="36"/>
       <c r="U193" s="36"/>
       <c r="V193" s="9"/>
@@ -36553,7 +36552,7 @@
       <c r="P194" s="9"/>
       <c r="Q194" s="9"/>
       <c r="R194" s="9"/>
-      <c r="S194" s="46"/>
+      <c r="S194" s="45"/>
       <c r="T194" s="36"/>
       <c r="U194" s="36"/>
       <c r="V194" s="9"/>
@@ -36635,7 +36634,7 @@
       <c r="P195" s="9"/>
       <c r="Q195" s="9"/>
       <c r="R195" s="9"/>
-      <c r="S195" s="46"/>
+      <c r="S195" s="45"/>
       <c r="T195" s="36"/>
       <c r="U195" s="36"/>
       <c r="V195" s="9"/>
@@ -36717,7 +36716,7 @@
       <c r="P196" s="9"/>
       <c r="Q196" s="9"/>
       <c r="R196" s="9"/>
-      <c r="S196" s="46"/>
+      <c r="S196" s="45"/>
       <c r="T196" s="36"/>
       <c r="U196" s="36"/>
       <c r="V196" s="9"/>
@@ -36799,7 +36798,7 @@
       <c r="P197" s="9"/>
       <c r="Q197" s="9"/>
       <c r="R197" s="9"/>
-      <c r="S197" s="46"/>
+      <c r="S197" s="45"/>
       <c r="T197" s="36"/>
       <c r="U197" s="36"/>
       <c r="V197" s="9"/>
@@ -36881,7 +36880,7 @@
       <c r="P198" s="9"/>
       <c r="Q198" s="9"/>
       <c r="R198" s="9"/>
-      <c r="S198" s="46"/>
+      <c r="S198" s="45"/>
       <c r="T198" s="36"/>
       <c r="U198" s="36"/>
       <c r="V198" s="9"/>
@@ -36963,7 +36962,7 @@
       <c r="P199" s="9"/>
       <c r="Q199" s="9"/>
       <c r="R199" s="9"/>
-      <c r="S199" s="46"/>
+      <c r="S199" s="45"/>
       <c r="T199" s="36"/>
       <c r="U199" s="36"/>
       <c r="V199" s="9"/>
@@ -37045,7 +37044,7 @@
       <c r="P200" s="9"/>
       <c r="Q200" s="9"/>
       <c r="R200" s="9"/>
-      <c r="S200" s="46"/>
+      <c r="S200" s="45"/>
       <c r="T200" s="36"/>
       <c r="U200" s="36"/>
       <c r="V200" s="9"/>
@@ -37127,7 +37126,7 @@
       <c r="P201" s="9"/>
       <c r="Q201" s="9"/>
       <c r="R201" s="9"/>
-      <c r="S201" s="46"/>
+      <c r="S201" s="45"/>
       <c r="T201" s="36"/>
       <c r="U201" s="36"/>
       <c r="V201" s="9"/>
@@ -37209,7 +37208,7 @@
       <c r="P202" s="9"/>
       <c r="Q202" s="9"/>
       <c r="R202" s="9"/>
-      <c r="S202" s="46"/>
+      <c r="S202" s="45"/>
       <c r="T202" s="36"/>
       <c r="U202" s="36"/>
       <c r="V202" s="9"/>
@@ -37291,7 +37290,7 @@
       <c r="P203" s="9"/>
       <c r="Q203" s="9"/>
       <c r="R203" s="9"/>
-      <c r="S203" s="46"/>
+      <c r="S203" s="45"/>
       <c r="T203" s="36"/>
       <c r="U203" s="36"/>
       <c r="V203" s="9"/>
@@ -37373,7 +37372,7 @@
       <c r="P204" s="9"/>
       <c r="Q204" s="9"/>
       <c r="R204" s="9"/>
-      <c r="S204" s="46"/>
+      <c r="S204" s="45"/>
       <c r="T204" s="36"/>
       <c r="U204" s="36"/>
       <c r="V204" s="9"/>
@@ -37455,7 +37454,7 @@
       <c r="P205" s="9"/>
       <c r="Q205" s="9"/>
       <c r="R205" s="9"/>
-      <c r="S205" s="46"/>
+      <c r="S205" s="45"/>
       <c r="T205" s="36"/>
       <c r="U205" s="36"/>
       <c r="V205" s="9"/>
@@ -37537,7 +37536,7 @@
       <c r="P206" s="9"/>
       <c r="Q206" s="9"/>
       <c r="R206" s="9"/>
-      <c r="S206" s="46"/>
+      <c r="S206" s="45"/>
       <c r="T206" s="36"/>
       <c r="U206" s="36"/>
       <c r="V206" s="9"/>
@@ -37619,7 +37618,7 @@
       <c r="P207" s="9"/>
       <c r="Q207" s="9"/>
       <c r="R207" s="9"/>
-      <c r="S207" s="46"/>
+      <c r="S207" s="45"/>
       <c r="T207" s="36"/>
       <c r="U207" s="36"/>
       <c r="V207" s="9"/>
@@ -37701,7 +37700,7 @@
       <c r="P208" s="9"/>
       <c r="Q208" s="9"/>
       <c r="R208" s="9"/>
-      <c r="S208" s="46"/>
+      <c r="S208" s="45"/>
       <c r="T208" s="36"/>
       <c r="U208" s="36"/>
       <c r="V208" s="9"/>
@@ -37783,7 +37782,7 @@
       <c r="P209" s="9"/>
       <c r="Q209" s="9"/>
       <c r="R209" s="9"/>
-      <c r="S209" s="46"/>
+      <c r="S209" s="45"/>
       <c r="T209" s="36"/>
       <c r="U209" s="36"/>
       <c r="V209" s="9"/>
@@ -37865,7 +37864,7 @@
       <c r="P210" s="9"/>
       <c r="Q210" s="9"/>
       <c r="R210" s="9"/>
-      <c r="S210" s="46"/>
+      <c r="S210" s="45"/>
       <c r="T210" s="36"/>
       <c r="U210" s="36"/>
       <c r="V210" s="9"/>
@@ -37947,7 +37946,7 @@
       <c r="P211" s="9"/>
       <c r="Q211" s="9"/>
       <c r="R211" s="9"/>
-      <c r="S211" s="46"/>
+      <c r="S211" s="45"/>
       <c r="T211" s="36"/>
       <c r="U211" s="36"/>
       <c r="V211" s="9"/>
@@ -38029,7 +38028,7 @@
       <c r="P212" s="9"/>
       <c r="Q212" s="9"/>
       <c r="R212" s="9"/>
-      <c r="S212" s="46"/>
+      <c r="S212" s="45"/>
       <c r="T212" s="36"/>
       <c r="U212" s="36"/>
       <c r="V212" s="9"/>
@@ -38111,7 +38110,7 @@
       <c r="P213" s="9"/>
       <c r="Q213" s="9"/>
       <c r="R213" s="9"/>
-      <c r="S213" s="46"/>
+      <c r="S213" s="45"/>
       <c r="T213" s="36"/>
       <c r="U213" s="36"/>
       <c r="V213" s="9"/>
@@ -38193,7 +38192,7 @@
       <c r="P214" s="9"/>
       <c r="Q214" s="9"/>
       <c r="R214" s="9"/>
-      <c r="S214" s="46"/>
+      <c r="S214" s="45"/>
       <c r="T214" s="36"/>
       <c r="U214" s="36"/>
       <c r="V214" s="9"/>
@@ -38275,7 +38274,7 @@
       <c r="P215" s="9"/>
       <c r="Q215" s="9"/>
       <c r="R215" s="9"/>
-      <c r="S215" s="46"/>
+      <c r="S215" s="45"/>
       <c r="T215" s="36"/>
       <c r="U215" s="36"/>
       <c r="V215" s="9"/>
@@ -38357,7 +38356,7 @@
       <c r="P216" s="9"/>
       <c r="Q216" s="9"/>
       <c r="R216" s="9"/>
-      <c r="S216" s="46"/>
+      <c r="S216" s="45"/>
       <c r="T216" s="36"/>
       <c r="U216" s="36"/>
       <c r="V216" s="9"/>
@@ -38439,7 +38438,7 @@
       <c r="P217" s="9"/>
       <c r="Q217" s="9"/>
       <c r="R217" s="9"/>
-      <c r="S217" s="46"/>
+      <c r="S217" s="45"/>
       <c r="T217" s="36"/>
       <c r="U217" s="36"/>
       <c r="V217" s="9"/>
@@ -38521,7 +38520,7 @@
       <c r="P218" s="9"/>
       <c r="Q218" s="9"/>
       <c r="R218" s="9"/>
-      <c r="S218" s="46"/>
+      <c r="S218" s="45"/>
       <c r="T218" s="36"/>
       <c r="U218" s="36"/>
       <c r="V218" s="9"/>
@@ -38603,7 +38602,7 @@
       <c r="P219" s="9"/>
       <c r="Q219" s="9"/>
       <c r="R219" s="9"/>
-      <c r="S219" s="46"/>
+      <c r="S219" s="45"/>
       <c r="T219" s="36"/>
       <c r="U219" s="36"/>
       <c r="V219" s="9"/>
@@ -38685,7 +38684,7 @@
       <c r="P220" s="9"/>
       <c r="Q220" s="9"/>
       <c r="R220" s="9"/>
-      <c r="S220" s="46"/>
+      <c r="S220" s="45"/>
       <c r="T220" s="36"/>
       <c r="U220" s="36"/>
       <c r="V220" s="9"/>
@@ -38767,7 +38766,7 @@
       <c r="P221" s="9"/>
       <c r="Q221" s="9"/>
       <c r="R221" s="9"/>
-      <c r="S221" s="46"/>
+      <c r="S221" s="45"/>
       <c r="T221" s="36"/>
       <c r="U221" s="36"/>
       <c r="V221" s="9"/>
@@ -38849,7 +38848,7 @@
       <c r="P222" s="9"/>
       <c r="Q222" s="9"/>
       <c r="R222" s="9"/>
-      <c r="S222" s="46"/>
+      <c r="S222" s="45"/>
       <c r="T222" s="36"/>
       <c r="U222" s="36"/>
       <c r="V222" s="9"/>
@@ -38931,7 +38930,7 @@
       <c r="P223" s="9"/>
       <c r="Q223" s="9"/>
       <c r="R223" s="9"/>
-      <c r="S223" s="46"/>
+      <c r="S223" s="45"/>
       <c r="T223" s="36"/>
       <c r="U223" s="36"/>
       <c r="V223" s="9"/>
@@ -39013,7 +39012,7 @@
       <c r="P224" s="9"/>
       <c r="Q224" s="9"/>
       <c r="R224" s="9"/>
-      <c r="S224" s="46"/>
+      <c r="S224" s="45"/>
       <c r="T224" s="36"/>
       <c r="U224" s="36"/>
       <c r="V224" s="9"/>
@@ -39095,7 +39094,7 @@
       <c r="P225" s="9"/>
       <c r="Q225" s="9"/>
       <c r="R225" s="9"/>
-      <c r="S225" s="46"/>
+      <c r="S225" s="45"/>
       <c r="T225" s="36"/>
       <c r="U225" s="36"/>
       <c r="V225" s="9"/>
@@ -39177,7 +39176,7 @@
       <c r="P226" s="9"/>
       <c r="Q226" s="9"/>
       <c r="R226" s="9"/>
-      <c r="S226" s="46"/>
+      <c r="S226" s="45"/>
       <c r="T226" s="36"/>
       <c r="U226" s="36"/>
       <c r="V226" s="9"/>
@@ -39259,7 +39258,7 @@
       <c r="P227" s="9"/>
       <c r="Q227" s="9"/>
       <c r="R227" s="9"/>
-      <c r="S227" s="46"/>
+      <c r="S227" s="45"/>
       <c r="T227" s="36"/>
       <c r="U227" s="36"/>
       <c r="V227" s="9"/>
@@ -39341,7 +39340,7 @@
       <c r="P228" s="9"/>
       <c r="Q228" s="9"/>
       <c r="R228" s="9"/>
-      <c r="S228" s="46"/>
+      <c r="S228" s="45"/>
       <c r="T228" s="36"/>
       <c r="U228" s="36"/>
       <c r="V228" s="9"/>
@@ -39423,7 +39422,7 @@
       <c r="P229" s="9"/>
       <c r="Q229" s="9"/>
       <c r="R229" s="9"/>
-      <c r="S229" s="46"/>
+      <c r="S229" s="45"/>
       <c r="T229" s="36"/>
       <c r="U229" s="36"/>
       <c r="V229" s="9"/>
@@ -39505,7 +39504,7 @@
       <c r="P230" s="9"/>
       <c r="Q230" s="9"/>
       <c r="R230" s="9"/>
-      <c r="S230" s="46"/>
+      <c r="S230" s="45"/>
       <c r="T230" s="36"/>
       <c r="U230" s="36"/>
       <c r="V230" s="9"/>
@@ -39587,7 +39586,7 @@
       <c r="P231" s="9"/>
       <c r="Q231" s="9"/>
       <c r="R231" s="9"/>
-      <c r="S231" s="46"/>
+      <c r="S231" s="45"/>
       <c r="T231" s="36"/>
       <c r="U231" s="36"/>
       <c r="V231" s="9"/>
@@ -39669,7 +39668,7 @@
       <c r="P232" s="9"/>
       <c r="Q232" s="9"/>
       <c r="R232" s="9"/>
-      <c r="S232" s="46"/>
+      <c r="S232" s="45"/>
       <c r="T232" s="36"/>
       <c r="U232" s="36"/>
       <c r="V232" s="9"/>
@@ -39751,7 +39750,7 @@
       <c r="P233" s="9"/>
       <c r="Q233" s="9"/>
       <c r="R233" s="9"/>
-      <c r="S233" s="46"/>
+      <c r="S233" s="45"/>
       <c r="T233" s="36"/>
       <c r="U233" s="36"/>
       <c r="V233" s="9"/>
@@ -39833,7 +39832,7 @@
       <c r="P234" s="9"/>
       <c r="Q234" s="9"/>
       <c r="R234" s="9"/>
-      <c r="S234" s="46"/>
+      <c r="S234" s="45"/>
       <c r="T234" s="36"/>
       <c r="U234" s="36"/>
       <c r="V234" s="9"/>
@@ -39915,7 +39914,7 @@
       <c r="P235" s="9"/>
       <c r="Q235" s="9"/>
       <c r="R235" s="9"/>
-      <c r="S235" s="46"/>
+      <c r="S235" s="45"/>
       <c r="T235" s="36"/>
       <c r="U235" s="36"/>
       <c r="V235" s="9"/>
@@ -39997,7 +39996,7 @@
       <c r="P236" s="9"/>
       <c r="Q236" s="9"/>
       <c r="R236" s="9"/>
-      <c r="S236" s="46"/>
+      <c r="S236" s="45"/>
       <c r="T236" s="36"/>
       <c r="U236" s="36"/>
       <c r="V236" s="9"/>
@@ -40079,7 +40078,7 @@
       <c r="P237" s="9"/>
       <c r="Q237" s="9"/>
       <c r="R237" s="9"/>
-      <c r="S237" s="46"/>
+      <c r="S237" s="45"/>
       <c r="T237" s="36"/>
       <c r="U237" s="36"/>
       <c r="V237" s="9"/>
@@ -40161,7 +40160,7 @@
       <c r="P238" s="9"/>
       <c r="Q238" s="9"/>
       <c r="R238" s="9"/>
-      <c r="S238" s="46"/>
+      <c r="S238" s="45"/>
       <c r="T238" s="36"/>
       <c r="U238" s="36"/>
       <c r="V238" s="9"/>
@@ -40243,7 +40242,7 @@
       <c r="P239" s="9"/>
       <c r="Q239" s="9"/>
       <c r="R239" s="9"/>
-      <c r="S239" s="46"/>
+      <c r="S239" s="45"/>
       <c r="T239" s="36"/>
       <c r="U239" s="36"/>
       <c r="V239" s="9"/>
@@ -40325,7 +40324,7 @@
       <c r="P240" s="9"/>
       <c r="Q240" s="9"/>
       <c r="R240" s="9"/>
-      <c r="S240" s="46"/>
+      <c r="S240" s="45"/>
       <c r="T240" s="36"/>
       <c r="U240" s="36"/>
       <c r="V240" s="9"/>
@@ -40407,7 +40406,7 @@
       <c r="P241" s="9"/>
       <c r="Q241" s="9"/>
       <c r="R241" s="9"/>
-      <c r="S241" s="46"/>
+      <c r="S241" s="45"/>
       <c r="T241" s="36"/>
       <c r="U241" s="36"/>
       <c r="V241" s="9"/>
@@ -40489,7 +40488,7 @@
       <c r="P242" s="9"/>
       <c r="Q242" s="9"/>
       <c r="R242" s="9"/>
-      <c r="S242" s="46"/>
+      <c r="S242" s="45"/>
       <c r="T242" s="36"/>
       <c r="U242" s="36"/>
       <c r="V242" s="9"/>
@@ -40571,7 +40570,7 @@
       <c r="P243" s="9"/>
       <c r="Q243" s="9"/>
       <c r="R243" s="9"/>
-      <c r="S243" s="46"/>
+      <c r="S243" s="45"/>
       <c r="T243" s="36"/>
       <c r="U243" s="36"/>
       <c r="V243" s="9"/>
@@ -40653,7 +40652,7 @@
       <c r="P244" s="9"/>
       <c r="Q244" s="9"/>
       <c r="R244" s="9"/>
-      <c r="S244" s="46"/>
+      <c r="S244" s="45"/>
       <c r="T244" s="36"/>
       <c r="U244" s="36"/>
       <c r="V244" s="9"/>
@@ -40735,7 +40734,7 @@
       <c r="P245" s="9"/>
       <c r="Q245" s="9"/>
       <c r="R245" s="9"/>
-      <c r="S245" s="46"/>
+      <c r="S245" s="45"/>
       <c r="T245" s="36"/>
       <c r="U245" s="36"/>
       <c r="V245" s="9"/>
@@ -40817,7 +40816,7 @@
       <c r="P246" s="9"/>
       <c r="Q246" s="9"/>
       <c r="R246" s="9"/>
-      <c r="S246" s="46"/>
+      <c r="S246" s="45"/>
       <c r="T246" s="36"/>
       <c r="U246" s="36"/>
       <c r="V246" s="9"/>
@@ -40899,7 +40898,7 @@
       <c r="P247" s="9"/>
       <c r="Q247" s="9"/>
       <c r="R247" s="9"/>
-      <c r="S247" s="46"/>
+      <c r="S247" s="45"/>
       <c r="T247" s="36"/>
       <c r="U247" s="36"/>
       <c r="V247" s="9"/>
@@ -40981,7 +40980,7 @@
       <c r="P248" s="9"/>
       <c r="Q248" s="9"/>
       <c r="R248" s="9"/>
-      <c r="S248" s="46"/>
+      <c r="S248" s="45"/>
       <c r="T248" s="36"/>
       <c r="U248" s="36"/>
       <c r="V248" s="9"/>
@@ -41063,7 +41062,7 @@
       <c r="P249" s="9"/>
       <c r="Q249" s="9"/>
       <c r="R249" s="9"/>
-      <c r="S249" s="46"/>
+      <c r="S249" s="45"/>
       <c r="T249" s="36"/>
       <c r="U249" s="36"/>
       <c r="V249" s="9"/>
@@ -41145,7 +41144,7 @@
       <c r="P250" s="9"/>
       <c r="Q250" s="9"/>
       <c r="R250" s="9"/>
-      <c r="S250" s="46"/>
+      <c r="S250" s="45"/>
       <c r="T250" s="36"/>
       <c r="U250" s="36"/>
       <c r="V250" s="9"/>
@@ -41227,7 +41226,7 @@
       <c r="P251" s="9"/>
       <c r="Q251" s="9"/>
       <c r="R251" s="9"/>
-      <c r="S251" s="46"/>
+      <c r="S251" s="45"/>
       <c r="T251" s="36"/>
       <c r="U251" s="36"/>
       <c r="V251" s="9"/>
@@ -41309,7 +41308,7 @@
       <c r="P252" s="9"/>
       <c r="Q252" s="9"/>
       <c r="R252" s="9"/>
-      <c r="S252" s="46"/>
+      <c r="S252" s="45"/>
       <c r="T252" s="36"/>
       <c r="U252" s="36"/>
       <c r="V252" s="9"/>
@@ -41391,7 +41390,7 @@
       <c r="P253" s="9"/>
       <c r="Q253" s="9"/>
       <c r="R253" s="9"/>
-      <c r="S253" s="46"/>
+      <c r="S253" s="45"/>
       <c r="T253" s="36"/>
       <c r="U253" s="36"/>
       <c r="V253" s="9"/>
@@ -41473,7 +41472,7 @@
       <c r="P254" s="9"/>
       <c r="Q254" s="9"/>
       <c r="R254" s="9"/>
-      <c r="S254" s="46"/>
+      <c r="S254" s="45"/>
       <c r="T254" s="36"/>
       <c r="U254" s="36"/>
       <c r="V254" s="9"/>
@@ -41555,7 +41554,7 @@
       <c r="P255" s="9"/>
       <c r="Q255" s="9"/>
       <c r="R255" s="9"/>
-      <c r="S255" s="46"/>
+      <c r="S255" s="45"/>
       <c r="T255" s="36"/>
       <c r="U255" s="36"/>
       <c r="V255" s="9"/>
@@ -41637,7 +41636,7 @@
       <c r="P256" s="9"/>
       <c r="Q256" s="9"/>
       <c r="R256" s="9"/>
-      <c r="S256" s="46"/>
+      <c r="S256" s="45"/>
       <c r="T256" s="36"/>
       <c r="U256" s="36"/>
       <c r="V256" s="9"/>
@@ -41719,7 +41718,7 @@
       <c r="P257" s="9"/>
       <c r="Q257" s="9"/>
       <c r="R257" s="9"/>
-      <c r="S257" s="46"/>
+      <c r="S257" s="45"/>
       <c r="T257" s="36"/>
       <c r="U257" s="36"/>
       <c r="V257" s="9"/>
@@ -41801,7 +41800,7 @@
       <c r="P258" s="9"/>
       <c r="Q258" s="9"/>
       <c r="R258" s="9"/>
-      <c r="S258" s="46"/>
+      <c r="S258" s="45"/>
       <c r="T258" s="36"/>
       <c r="U258" s="36"/>
       <c r="V258" s="9"/>
@@ -41883,7 +41882,7 @@
       <c r="P259" s="9"/>
       <c r="Q259" s="9"/>
       <c r="R259" s="9"/>
-      <c r="S259" s="46"/>
+      <c r="S259" s="45"/>
       <c r="T259" s="36"/>
       <c r="U259" s="36"/>
       <c r="V259" s="9"/>
@@ -41965,7 +41964,7 @@
       <c r="P260" s="9"/>
       <c r="Q260" s="9"/>
       <c r="R260" s="9"/>
-      <c r="S260" s="46"/>
+      <c r="S260" s="45"/>
       <c r="T260" s="36"/>
       <c r="U260" s="36"/>
       <c r="V260" s="9"/>
@@ -42047,7 +42046,7 @@
       <c r="P261" s="9"/>
       <c r="Q261" s="9"/>
       <c r="R261" s="9"/>
-      <c r="S261" s="46"/>
+      <c r="S261" s="45"/>
       <c r="T261" s="36"/>
       <c r="U261" s="36"/>
       <c r="V261" s="9"/>
@@ -42129,7 +42128,7 @@
       <c r="P262" s="9"/>
       <c r="Q262" s="9"/>
       <c r="R262" s="9"/>
-      <c r="S262" s="46"/>
+      <c r="S262" s="45"/>
       <c r="T262" s="36"/>
       <c r="U262" s="36"/>
       <c r="V262" s="9"/>
@@ -42211,7 +42210,7 @@
       <c r="P263" s="9"/>
       <c r="Q263" s="9"/>
       <c r="R263" s="9"/>
-      <c r="S263" s="46"/>
+      <c r="S263" s="45"/>
       <c r="T263" s="36"/>
       <c r="U263" s="36"/>
       <c r="V263" s="9"/>
@@ -42293,7 +42292,7 @@
       <c r="P264" s="9"/>
       <c r="Q264" s="9"/>
       <c r="R264" s="9"/>
-      <c r="S264" s="46"/>
+      <c r="S264" s="45"/>
       <c r="T264" s="36"/>
       <c r="U264" s="36"/>
       <c r="V264" s="9"/>
@@ -42375,7 +42374,7 @@
       <c r="P265" s="9"/>
       <c r="Q265" s="9"/>
       <c r="R265" s="9"/>
-      <c r="S265" s="46"/>
+      <c r="S265" s="45"/>
       <c r="T265" s="36"/>
       <c r="U265" s="36"/>
       <c r="V265" s="9"/>
@@ -42457,7 +42456,7 @@
       <c r="P266" s="9"/>
       <c r="Q266" s="9"/>
       <c r="R266" s="9"/>
-      <c r="S266" s="46"/>
+      <c r="S266" s="45"/>
       <c r="T266" s="36"/>
       <c r="U266" s="36"/>
       <c r="V266" s="9"/>
@@ -42539,7 +42538,7 @@
       <c r="P267" s="9"/>
       <c r="Q267" s="9"/>
       <c r="R267" s="9"/>
-      <c r="S267" s="46"/>
+      <c r="S267" s="45"/>
       <c r="T267" s="36"/>
       <c r="U267" s="36"/>
       <c r="V267" s="9"/>
@@ -42621,7 +42620,7 @@
       <c r="P268" s="9"/>
       <c r="Q268" s="9"/>
       <c r="R268" s="9"/>
-      <c r="S268" s="46"/>
+      <c r="S268" s="45"/>
       <c r="T268" s="36"/>
       <c r="U268" s="36"/>
       <c r="V268" s="9"/>
@@ -42703,7 +42702,7 @@
       <c r="P269" s="9"/>
       <c r="Q269" s="9"/>
       <c r="R269" s="9"/>
-      <c r="S269" s="46"/>
+      <c r="S269" s="45"/>
       <c r="T269" s="36"/>
       <c r="U269" s="36"/>
       <c r="V269" s="9"/>
@@ -42785,7 +42784,7 @@
       <c r="P270" s="9"/>
       <c r="Q270" s="9"/>
       <c r="R270" s="9"/>
-      <c r="S270" s="46"/>
+      <c r="S270" s="45"/>
       <c r="T270" s="36"/>
       <c r="U270" s="36"/>
       <c r="V270" s="9"/>
@@ -42867,7 +42866,7 @@
       <c r="P271" s="9"/>
       <c r="Q271" s="9"/>
       <c r="R271" s="9"/>
-      <c r="S271" s="46"/>
+      <c r="S271" s="45"/>
       <c r="T271" s="36"/>
       <c r="U271" s="36"/>
       <c r="V271" s="9"/>
@@ -42949,7 +42948,7 @@
       <c r="P272" s="9"/>
       <c r="Q272" s="9"/>
       <c r="R272" s="9"/>
-      <c r="S272" s="46"/>
+      <c r="S272" s="45"/>
       <c r="T272" s="36"/>
       <c r="U272" s="36"/>
       <c r="V272" s="9"/>
@@ -43031,7 +43030,7 @@
       <c r="P273" s="9"/>
       <c r="Q273" s="9"/>
       <c r="R273" s="9"/>
-      <c r="S273" s="46"/>
+      <c r="S273" s="45"/>
       <c r="T273" s="36"/>
       <c r="U273" s="36"/>
       <c r="V273" s="9"/>
@@ -43113,7 +43112,7 @@
       <c r="P274" s="9"/>
       <c r="Q274" s="9"/>
       <c r="R274" s="9"/>
-      <c r="S274" s="46"/>
+      <c r="S274" s="45"/>
       <c r="T274" s="36"/>
       <c r="U274" s="36"/>
       <c r="V274" s="9"/>
@@ -43195,7 +43194,7 @@
       <c r="P275" s="9"/>
       <c r="Q275" s="9"/>
       <c r="R275" s="9"/>
-      <c r="S275" s="46"/>
+      <c r="S275" s="45"/>
       <c r="T275" s="36"/>
       <c r="U275" s="36"/>
       <c r="V275" s="9"/>
@@ -43277,7 +43276,7 @@
       <c r="P276" s="9"/>
       <c r="Q276" s="9"/>
       <c r="R276" s="9"/>
-      <c r="S276" s="46"/>
+      <c r="S276" s="45"/>
       <c r="T276" s="36"/>
       <c r="U276" s="36"/>
       <c r="V276" s="9"/>
@@ -43359,7 +43358,7 @@
       <c r="P277" s="9"/>
       <c r="Q277" s="9"/>
       <c r="R277" s="9"/>
-      <c r="S277" s="46"/>
+      <c r="S277" s="45"/>
       <c r="T277" s="36"/>
       <c r="U277" s="36"/>
       <c r="V277" s="9"/>
@@ -43441,7 +43440,7 @@
       <c r="P278" s="9"/>
       <c r="Q278" s="9"/>
       <c r="R278" s="9"/>
-      <c r="S278" s="46"/>
+      <c r="S278" s="45"/>
       <c r="T278" s="36"/>
       <c r="U278" s="36"/>
       <c r="V278" s="9"/>
@@ -43523,7 +43522,7 @@
       <c r="P279" s="9"/>
       <c r="Q279" s="9"/>
       <c r="R279" s="9"/>
-      <c r="S279" s="46"/>
+      <c r="S279" s="45"/>
       <c r="T279" s="36"/>
       <c r="U279" s="36"/>
       <c r="V279" s="9"/>
@@ -43605,7 +43604,7 @@
       <c r="P280" s="9"/>
       <c r="Q280" s="9"/>
       <c r="R280" s="9"/>
-      <c r="S280" s="46"/>
+      <c r="S280" s="45"/>
       <c r="T280" s="36"/>
       <c r="U280" s="36"/>
       <c r="V280" s="9"/>
@@ -43687,7 +43686,7 @@
       <c r="P281" s="9"/>
       <c r="Q281" s="9"/>
       <c r="R281" s="9"/>
-      <c r="S281" s="46"/>
+      <c r="S281" s="45"/>
       <c r="T281" s="36"/>
       <c r="U281" s="36"/>
       <c r="V281" s="9"/>
@@ -43769,7 +43768,7 @@
       <c r="P282" s="9"/>
       <c r="Q282" s="9"/>
       <c r="R282" s="9"/>
-      <c r="S282" s="46"/>
+      <c r="S282" s="45"/>
       <c r="T282" s="36"/>
       <c r="U282" s="36"/>
       <c r="V282" s="9"/>
@@ -43851,7 +43850,7 @@
       <c r="P283" s="9"/>
       <c r="Q283" s="9"/>
       <c r="R283" s="9"/>
-      <c r="S283" s="46"/>
+      <c r="S283" s="45"/>
       <c r="T283" s="36"/>
       <c r="U283" s="36"/>
       <c r="V283" s="9"/>
@@ -43933,7 +43932,7 @@
       <c r="P284" s="9"/>
       <c r="Q284" s="9"/>
       <c r="R284" s="9"/>
-      <c r="S284" s="46"/>
+      <c r="S284" s="45"/>
       <c r="T284" s="36"/>
       <c r="U284" s="36"/>
       <c r="V284" s="9"/>
@@ -44015,7 +44014,7 @@
       <c r="P285" s="9"/>
       <c r="Q285" s="9"/>
       <c r="R285" s="9"/>
-      <c r="S285" s="46"/>
+      <c r="S285" s="45"/>
       <c r="T285" s="36"/>
       <c r="U285" s="36"/>
       <c r="V285" s="9"/>
@@ -44097,7 +44096,7 @@
       <c r="P286" s="9"/>
       <c r="Q286" s="9"/>
       <c r="R286" s="9"/>
-      <c r="S286" s="46"/>
+      <c r="S286" s="45"/>
       <c r="T286" s="36"/>
       <c r="U286" s="36"/>
       <c r="V286" s="9"/>
@@ -44179,7 +44178,7 @@
       <c r="P287" s="9"/>
       <c r="Q287" s="9"/>
       <c r="R287" s="9"/>
-      <c r="S287" s="46"/>
+      <c r="S287" s="45"/>
       <c r="T287" s="36"/>
       <c r="U287" s="36"/>
       <c r="V287" s="9"/>
@@ -44261,7 +44260,7 @@
       <c r="P288" s="9"/>
       <c r="Q288" s="9"/>
       <c r="R288" s="9"/>
-      <c r="S288" s="46"/>
+      <c r="S288" s="45"/>
       <c r="T288" s="36"/>
       <c r="U288" s="36"/>
       <c r="V288" s="9"/>
@@ -44343,7 +44342,7 @@
       <c r="P289" s="9"/>
       <c r="Q289" s="9"/>
       <c r="R289" s="9"/>
-      <c r="S289" s="46"/>
+      <c r="S289" s="45"/>
       <c r="T289" s="36"/>
       <c r="U289" s="36"/>
       <c r="V289" s="9"/>
@@ -44425,7 +44424,7 @@
       <c r="P290" s="9"/>
       <c r="Q290" s="9"/>
       <c r="R290" s="9"/>
-      <c r="S290" s="46"/>
+      <c r="S290" s="45"/>
       <c r="T290" s="36"/>
       <c r="U290" s="36"/>
       <c r="V290" s="9"/>
@@ -44507,7 +44506,7 @@
       <c r="P291" s="9"/>
       <c r="Q291" s="9"/>
       <c r="R291" s="9"/>
-      <c r="S291" s="46"/>
+      <c r="S291" s="45"/>
       <c r="T291" s="36"/>
       <c r="U291" s="36"/>
       <c r="V291" s="9"/>
@@ -44589,7 +44588,7 @@
       <c r="P292" s="9"/>
       <c r="Q292" s="9"/>
       <c r="R292" s="9"/>
-      <c r="S292" s="46"/>
+      <c r="S292" s="45"/>
       <c r="T292" s="36"/>
       <c r="U292" s="36"/>
       <c r="V292" s="9"/>
@@ -44671,7 +44670,7 @@
       <c r="P293" s="9"/>
       <c r="Q293" s="9"/>
       <c r="R293" s="9"/>
-      <c r="S293" s="46"/>
+      <c r="S293" s="45"/>
       <c r="T293" s="36"/>
       <c r="U293" s="36"/>
       <c r="V293" s="9"/>
@@ -44753,7 +44752,7 @@
       <c r="P294" s="9"/>
       <c r="Q294" s="9"/>
       <c r="R294" s="9"/>
-      <c r="S294" s="46"/>
+      <c r="S294" s="45"/>
       <c r="T294" s="36"/>
       <c r="U294" s="36"/>
       <c r="V294" s="9"/>
@@ -44835,7 +44834,7 @@
       <c r="P295" s="9"/>
       <c r="Q295" s="9"/>
       <c r="R295" s="9"/>
-      <c r="S295" s="46"/>
+      <c r="S295" s="45"/>
       <c r="T295" s="36"/>
       <c r="U295" s="36"/>
       <c r="V295" s="9"/>
@@ -44917,7 +44916,7 @@
       <c r="P296" s="9"/>
       <c r="Q296" s="9"/>
       <c r="R296" s="9"/>
-      <c r="S296" s="46"/>
+      <c r="S296" s="45"/>
       <c r="T296" s="36"/>
       <c r="U296" s="36"/>
       <c r="V296" s="9"/>
@@ -44999,7 +44998,7 @@
       <c r="P297" s="9"/>
       <c r="Q297" s="9"/>
       <c r="R297" s="9"/>
-      <c r="S297" s="46"/>
+      <c r="S297" s="45"/>
       <c r="T297" s="36"/>
       <c r="U297" s="36"/>
       <c r="V297" s="9"/>
@@ -45081,7 +45080,7 @@
       <c r="P298" s="9"/>
       <c r="Q298" s="9"/>
       <c r="R298" s="9"/>
-      <c r="S298" s="46"/>
+      <c r="S298" s="45"/>
       <c r="T298" s="36"/>
       <c r="U298" s="36"/>
       <c r="V298" s="9"/>
@@ -45163,7 +45162,7 @@
       <c r="P299" s="9"/>
       <c r="Q299" s="9"/>
       <c r="R299" s="9"/>
-      <c r="S299" s="46"/>
+      <c r="S299" s="45"/>
       <c r="T299" s="36"/>
       <c r="U299" s="36"/>
       <c r="V299" s="9"/>
@@ -45245,7 +45244,7 @@
       <c r="P300" s="9"/>
       <c r="Q300" s="9"/>
       <c r="R300" s="9"/>
-      <c r="S300" s="46"/>
+      <c r="S300" s="45"/>
       <c r="T300" s="36"/>
       <c r="U300" s="36"/>
       <c r="V300" s="9"/>
@@ -45327,7 +45326,7 @@
       <c r="P301" s="9"/>
       <c r="Q301" s="9"/>
       <c r="R301" s="9"/>
-      <c r="S301" s="46"/>
+      <c r="S301" s="45"/>
       <c r="T301" s="36"/>
       <c r="U301" s="36"/>
       <c r="V301" s="9"/>
@@ -45409,7 +45408,7 @@
       <c r="P302" s="9"/>
       <c r="Q302" s="9"/>
       <c r="R302" s="9"/>
-      <c r="S302" s="46"/>
+      <c r="S302" s="45"/>
       <c r="T302" s="36"/>
       <c r="U302" s="36"/>
       <c r="V302" s="9"/>
@@ -45491,7 +45490,7 @@
       <c r="P303" s="9"/>
       <c r="Q303" s="9"/>
       <c r="R303" s="9"/>
-      <c r="S303" s="46"/>
+      <c r="S303" s="45"/>
       <c r="T303" s="36"/>
       <c r="U303" s="36"/>
       <c r="V303" s="9"/>
@@ -45573,7 +45572,7 @@
       <c r="P304" s="9"/>
       <c r="Q304" s="9"/>
       <c r="R304" s="9"/>
-      <c r="S304" s="46"/>
+      <c r="S304" s="45"/>
       <c r="T304" s="36"/>
       <c r="U304" s="36"/>
       <c r="V304" s="9"/>
@@ -45655,7 +45654,7 @@
       <c r="P305" s="9"/>
       <c r="Q305" s="9"/>
       <c r="R305" s="9"/>
-      <c r="S305" s="46"/>
+      <c r="S305" s="45"/>
       <c r="T305" s="36"/>
       <c r="U305" s="36"/>
       <c r="V305" s="9"/>
@@ -45737,7 +45736,7 @@
       <c r="P306" s="9"/>
       <c r="Q306" s="9"/>
       <c r="R306" s="9"/>
-      <c r="S306" s="46"/>
+      <c r="S306" s="45"/>
       <c r="T306" s="36"/>
       <c r="U306" s="36"/>
       <c r="V306" s="9"/>
@@ -45819,7 +45818,7 @@
       <c r="P307" s="9"/>
       <c r="Q307" s="9"/>
       <c r="R307" s="9"/>
-      <c r="S307" s="46"/>
+      <c r="S307" s="45"/>
       <c r="T307" s="36"/>
       <c r="U307" s="36"/>
       <c r="V307" s="9"/>
@@ -45901,7 +45900,7 @@
       <c r="P308" s="9"/>
       <c r="Q308" s="9"/>
       <c r="R308" s="9"/>
-      <c r="S308" s="46"/>
+      <c r="S308" s="45"/>
       <c r="T308" s="36"/>
       <c r="U308" s="36"/>
       <c r="V308" s="9"/>
@@ -45983,7 +45982,7 @@
       <c r="P309" s="9"/>
       <c r="Q309" s="9"/>
       <c r="R309" s="9"/>
-      <c r="S309" s="46"/>
+      <c r="S309" s="45"/>
       <c r="T309" s="36"/>
       <c r="U309" s="36"/>
       <c r="V309" s="9"/>
@@ -46065,7 +46064,7 @@
       <c r="P310" s="9"/>
       <c r="Q310" s="9"/>
       <c r="R310" s="9"/>
-      <c r="S310" s="46"/>
+      <c r="S310" s="45"/>
       <c r="T310" s="36"/>
       <c r="U310" s="36"/>
       <c r="V310" s="9"/>
@@ -46147,7 +46146,7 @@
       <c r="P311" s="9"/>
       <c r="Q311" s="9"/>
       <c r="R311" s="9"/>
-      <c r="S311" s="46"/>
+      <c r="S311" s="45"/>
       <c r="T311" s="36"/>
       <c r="U311" s="36"/>
       <c r="V311" s="9"/>
@@ -46229,7 +46228,7 @@
       <c r="P312" s="9"/>
       <c r="Q312" s="9"/>
       <c r="R312" s="9"/>
-      <c r="S312" s="46"/>
+      <c r="S312" s="45"/>
       <c r="T312" s="36"/>
       <c r="U312" s="36"/>
       <c r="V312" s="9"/>
@@ -46311,7 +46310,7 @@
       <c r="P313" s="9"/>
       <c r="Q313" s="9"/>
       <c r="R313" s="9"/>
-      <c r="S313" s="46"/>
+      <c r="S313" s="45"/>
       <c r="T313" s="36"/>
       <c r="U313" s="36"/>
       <c r="V313" s="9"/>
@@ -46393,7 +46392,7 @@
       <c r="P314" s="9"/>
       <c r="Q314" s="9"/>
       <c r="R314" s="9"/>
-      <c r="S314" s="46"/>
+      <c r="S314" s="45"/>
       <c r="T314" s="36"/>
       <c r="U314" s="36"/>
       <c r="V314" s="9"/>
@@ -46475,7 +46474,7 @@
       <c r="P315" s="9"/>
       <c r="Q315" s="9"/>
       <c r="R315" s="9"/>
-      <c r="S315" s="46"/>
+      <c r="S315" s="45"/>
       <c r="T315" s="36"/>
       <c r="U315" s="36"/>
       <c r="V315" s="9"/>
@@ -46557,7 +46556,7 @@
       <c r="P316" s="9"/>
       <c r="Q316" s="9"/>
       <c r="R316" s="9"/>
-      <c r="S316" s="46"/>
+      <c r="S316" s="45"/>
       <c r="T316" s="36"/>
       <c r="U316" s="36"/>
       <c r="V316" s="9"/>
@@ -46639,7 +46638,7 @@
       <c r="P317" s="9"/>
       <c r="Q317" s="9"/>
       <c r="R317" s="9"/>
-      <c r="S317" s="46"/>
+      <c r="S317" s="45"/>
       <c r="T317" s="36"/>
       <c r="U317" s="36"/>
       <c r="V317" s="9"/>
@@ -46721,7 +46720,7 @@
       <c r="P318" s="9"/>
       <c r="Q318" s="9"/>
       <c r="R318" s="9"/>
-      <c r="S318" s="46"/>
+      <c r="S318" s="45"/>
       <c r="T318" s="36"/>
       <c r="U318" s="36"/>
       <c r="V318" s="9"/>
@@ -46803,7 +46802,7 @@
       <c r="P319" s="9"/>
       <c r="Q319" s="9"/>
       <c r="R319" s="9"/>
-      <c r="S319" s="46"/>
+      <c r="S319" s="45"/>
       <c r="T319" s="36"/>
       <c r="U319" s="36"/>
       <c r="V319" s="9"/>
@@ -46885,7 +46884,7 @@
       <c r="P320" s="9"/>
       <c r="Q320" s="9"/>
       <c r="R320" s="9"/>
-      <c r="S320" s="46"/>
+      <c r="S320" s="45"/>
       <c r="T320" s="36"/>
       <c r="U320" s="36"/>
       <c r="V320" s="9"/>
@@ -46967,7 +46966,7 @@
       <c r="P321" s="9"/>
       <c r="Q321" s="9"/>
       <c r="R321" s="9"/>
-      <c r="S321" s="46"/>
+      <c r="S321" s="45"/>
       <c r="T321" s="36"/>
       <c r="U321" s="36"/>
       <c r="V321" s="9"/>
@@ -47049,7 +47048,7 @@
       <c r="P322" s="9"/>
       <c r="Q322" s="9"/>
       <c r="R322" s="9"/>
-      <c r="S322" s="46"/>
+      <c r="S322" s="45"/>
       <c r="T322" s="36"/>
       <c r="U322" s="36"/>
       <c r="V322" s="9"/>
@@ -47131,7 +47130,7 @@
       <c r="P323" s="9"/>
       <c r="Q323" s="9"/>
       <c r="R323" s="9"/>
-      <c r="S323" s="46"/>
+      <c r="S323" s="45"/>
       <c r="T323" s="36"/>
       <c r="U323" s="36"/>
       <c r="V323" s="9"/>
@@ -47213,7 +47212,7 @@
       <c r="P324" s="9"/>
       <c r="Q324" s="9"/>
       <c r="R324" s="9"/>
-      <c r="S324" s="46"/>
+      <c r="S324" s="45"/>
       <c r="T324" s="36"/>
       <c r="U324" s="36"/>
       <c r="V324" s="9"/>
@@ -47295,7 +47294,7 @@
       <c r="P325" s="9"/>
       <c r="Q325" s="9"/>
       <c r="R325" s="9"/>
-      <c r="S325" s="46"/>
+      <c r="S325" s="45"/>
       <c r="T325" s="36"/>
       <c r="U325" s="36"/>
       <c r="V325" s="9"/>
@@ -47377,7 +47376,7 @@
       <c r="P326" s="9"/>
       <c r="Q326" s="9"/>
       <c r="R326" s="9"/>
-      <c r="S326" s="46"/>
+      <c r="S326" s="45"/>
       <c r="T326" s="36"/>
       <c r="U326" s="36"/>
       <c r="V326" s="9"/>
@@ -47459,7 +47458,7 @@
       <c r="P327" s="9"/>
       <c r="Q327" s="9"/>
       <c r="R327" s="9"/>
-      <c r="S327" s="46"/>
+      <c r="S327" s="45"/>
       <c r="T327" s="36"/>
       <c r="U327" s="36"/>
       <c r="V327" s="9"/>
@@ -47541,7 +47540,7 @@
       <c r="P328" s="9"/>
       <c r="Q328" s="9"/>
       <c r="R328" s="9"/>
-      <c r="S328" s="46"/>
+      <c r="S328" s="45"/>
       <c r="T328" s="36"/>
       <c r="U328" s="36"/>
       <c r="V328" s="9"/>
@@ -47623,7 +47622,7 @@
       <c r="P329" s="9"/>
       <c r="Q329" s="9"/>
       <c r="R329" s="9"/>
-      <c r="S329" s="46"/>
+      <c r="S329" s="45"/>
       <c r="T329" s="36"/>
       <c r="U329" s="36"/>
       <c r="V329" s="9"/>
@@ -47705,7 +47704,7 @@
       <c r="P330" s="9"/>
       <c r="Q330" s="9"/>
       <c r="R330" s="9"/>
-      <c r="S330" s="46"/>
+      <c r="S330" s="45"/>
       <c r="T330" s="36"/>
       <c r="U330" s="36"/>
       <c r="V330" s="9"/>
@@ -47787,7 +47786,7 @@
       <c r="P331" s="9"/>
       <c r="Q331" s="9"/>
       <c r="R331" s="9"/>
-      <c r="S331" s="46"/>
+      <c r="S331" s="45"/>
       <c r="T331" s="36"/>
       <c r="U331" s="36"/>
       <c r="V331" s="9"/>
@@ -47869,7 +47868,7 @@
       <c r="P332" s="9"/>
       <c r="Q332" s="9"/>
       <c r="R332" s="9"/>
-      <c r="S332" s="46"/>
+      <c r="S332" s="45"/>
       <c r="T332" s="36"/>
       <c r="U332" s="36"/>
       <c r="V332" s="9"/>
@@ -47951,7 +47950,7 @@
       <c r="P333" s="9"/>
       <c r="Q333" s="9"/>
       <c r="R333" s="9"/>
-      <c r="S333" s="46"/>
+      <c r="S333" s="45"/>
       <c r="T333" s="36"/>
       <c r="U333" s="36"/>
       <c r="V333" s="9"/>
@@ -48033,7 +48032,7 @@
       <c r="P334" s="9"/>
       <c r="Q334" s="9"/>
       <c r="R334" s="9"/>
-      <c r="S334" s="46"/>
+      <c r="S334" s="45"/>
       <c r="T334" s="36"/>
       <c r="U334" s="36"/>
       <c r="V334" s="9"/>
@@ -48115,7 +48114,7 @@
       <c r="P335" s="9"/>
       <c r="Q335" s="9"/>
       <c r="R335" s="9"/>
-      <c r="S335" s="46"/>
+      <c r="S335" s="45"/>
       <c r="T335" s="36"/>
       <c r="U335" s="36"/>
       <c r="V335" s="9"/>
@@ -48197,7 +48196,7 @@
       <c r="P336" s="9"/>
       <c r="Q336" s="9"/>
       <c r="R336" s="9"/>
-      <c r="S336" s="46"/>
+      <c r="S336" s="45"/>
       <c r="T336" s="36"/>
       <c r="U336" s="36"/>
       <c r="V336" s="9"/>
@@ -48279,7 +48278,7 @@
       <c r="P337" s="9"/>
       <c r="Q337" s="9"/>
       <c r="R337" s="9"/>
-      <c r="S337" s="46"/>
+      <c r="S337" s="45"/>
       <c r="T337" s="36"/>
       <c r="U337" s="36"/>
       <c r="V337" s="9"/>
@@ -48361,7 +48360,7 @@
       <c r="P338" s="9"/>
       <c r="Q338" s="9"/>
       <c r="R338" s="9"/>
-      <c r="S338" s="46"/>
+      <c r="S338" s="45"/>
       <c r="T338" s="36"/>
       <c r="U338" s="36"/>
       <c r="V338" s="9"/>
@@ -48443,7 +48442,7 @@
       <c r="P339" s="9"/>
       <c r="Q339" s="9"/>
       <c r="R339" s="9"/>
-      <c r="S339" s="46"/>
+      <c r="S339" s="45"/>
       <c r="T339" s="36"/>
       <c r="U339" s="36"/>
       <c r="V339" s="9"/>
@@ -48525,7 +48524,7 @@
       <c r="P340" s="9"/>
       <c r="Q340" s="9"/>
       <c r="R340" s="9"/>
-      <c r="S340" s="46"/>
+      <c r="S340" s="45"/>
       <c r="T340" s="36"/>
       <c r="U340" s="36"/>
       <c r="V340" s="9"/>
@@ -48607,7 +48606,7 @@
       <c r="P341" s="9"/>
       <c r="Q341" s="9"/>
       <c r="R341" s="9"/>
-      <c r="S341" s="46"/>
+      <c r="S341" s="45"/>
       <c r="T341" s="36"/>
       <c r="U341" s="36"/>
       <c r="V341" s="9"/>
@@ -48689,7 +48688,7 @@
       <c r="P342" s="9"/>
       <c r="Q342" s="9"/>
       <c r="R342" s="9"/>
-      <c r="S342" s="46"/>
+      <c r="S342" s="45"/>
       <c r="T342" s="36"/>
       <c r="U342" s="36"/>
       <c r="V342" s="9"/>
@@ -48771,7 +48770,7 @@
       <c r="P343" s="9"/>
       <c r="Q343" s="9"/>
       <c r="R343" s="9"/>
-      <c r="S343" s="46"/>
+      <c r="S343" s="45"/>
       <c r="T343" s="36"/>
       <c r="U343" s="36"/>
       <c r="V343" s="9"/>
@@ -48853,7 +48852,7 @@
       <c r="P344" s="9"/>
       <c r="Q344" s="9"/>
       <c r="R344" s="9"/>
-      <c r="S344" s="46"/>
+      <c r="S344" s="45"/>
       <c r="T344" s="36"/>
       <c r="U344" s="36"/>
       <c r="V344" s="9"/>
@@ -48935,7 +48934,7 @@
       <c r="P345" s="9"/>
       <c r="Q345" s="9"/>
       <c r="R345" s="9"/>
-      <c r="S345" s="46"/>
+      <c r="S345" s="45"/>
       <c r="T345" s="36"/>
       <c r="U345" s="36"/>
       <c r="V345" s="9"/>
@@ -49017,7 +49016,7 @@
       <c r="P346" s="9"/>
       <c r="Q346" s="9"/>
       <c r="R346" s="9"/>
-      <c r="S346" s="46"/>
+      <c r="S346" s="45"/>
       <c r="T346" s="36"/>
       <c r="U346" s="36"/>
       <c r="V346" s="9"/>
@@ -49099,7 +49098,7 @@
       <c r="P347" s="9"/>
       <c r="Q347" s="9"/>
       <c r="R347" s="9"/>
-      <c r="S347" s="46"/>
+      <c r="S347" s="45"/>
       <c r="T347" s="36"/>
       <c r="U347" s="36"/>
       <c r="V347" s="9"/>
@@ -49181,7 +49180,7 @@
       <c r="P348" s="9"/>
       <c r="Q348" s="9"/>
       <c r="R348" s="9"/>
-      <c r="S348" s="46"/>
+      <c r="S348" s="45"/>
       <c r="T348" s="36"/>
       <c r="U348" s="36"/>
       <c r="V348" s="9"/>
@@ -49263,7 +49262,7 @@
       <c r="P349" s="9"/>
       <c r="Q349" s="9"/>
       <c r="R349" s="9"/>
-      <c r="S349" s="46"/>
+      <c r="S349" s="45"/>
       <c r="T349" s="36"/>
       <c r="U349" s="36"/>
       <c r="V349" s="9"/>
@@ -49345,7 +49344,7 @@
       <c r="P350" s="9"/>
       <c r="Q350" s="9"/>
       <c r="R350" s="9"/>
-      <c r="S350" s="46"/>
+      <c r="S350" s="45"/>
       <c r="T350" s="36"/>
       <c r="U350" s="36"/>
       <c r="V350" s="9"/>
@@ -49427,7 +49426,7 @@
       <c r="P351" s="9"/>
       <c r="Q351" s="9"/>
       <c r="R351" s="9"/>
-      <c r="S351" s="46"/>
+      <c r="S351" s="45"/>
       <c r="T351" s="36"/>
       <c r="U351" s="36"/>
       <c r="V351" s="9"/>
@@ -49509,7 +49508,7 @@
       <c r="P352" s="9"/>
       <c r="Q352" s="9"/>
       <c r="R352" s="9"/>
-      <c r="S352" s="46"/>
+      <c r="S352" s="45"/>
       <c r="T352" s="36"/>
       <c r="U352" s="36"/>
       <c r="V352" s="9"/>
@@ -49591,7 +49590,7 @@
       <c r="P353" s="9"/>
       <c r="Q353" s="9"/>
       <c r="R353" s="9"/>
-      <c r="S353" s="46"/>
+      <c r="S353" s="45"/>
       <c r="T353" s="36"/>
       <c r="U353" s="36"/>
       <c r="V353" s="9"/>
@@ -49673,7 +49672,7 @@
       <c r="P354" s="9"/>
       <c r="Q354" s="9"/>
       <c r="R354" s="9"/>
-      <c r="S354" s="46"/>
+      <c r="S354" s="45"/>
       <c r="T354" s="36"/>
       <c r="U354" s="36"/>
       <c r="V354" s="9"/>
@@ -49755,7 +49754,7 @@
       <c r="P355" s="9"/>
       <c r="Q355" s="9"/>
       <c r="R355" s="9"/>
-      <c r="S355" s="46"/>
+      <c r="S355" s="45"/>
       <c r="T355" s="36"/>
       <c r="U355" s="36"/>
       <c r="V355" s="9"/>
@@ -49837,7 +49836,7 @@
       <c r="P356" s="9"/>
       <c r="Q356" s="9"/>
       <c r="R356" s="9"/>
-      <c r="S356" s="46"/>
+      <c r="S356" s="45"/>
       <c r="T356" s="36"/>
       <c r="U356" s="36"/>
       <c r="V356" s="9"/>
@@ -49919,7 +49918,7 @@
       <c r="P357" s="9"/>
       <c r="Q357" s="9"/>
       <c r="R357" s="9"/>
-      <c r="S357" s="46"/>
+      <c r="S357" s="45"/>
       <c r="T357" s="36"/>
       <c r="U357" s="36"/>
       <c r="V357" s="9"/>
@@ -50001,7 +50000,7 @@
       <c r="P358" s="9"/>
       <c r="Q358" s="9"/>
       <c r="R358" s="9"/>
-      <c r="S358" s="46"/>
+      <c r="S358" s="45"/>
       <c r="T358" s="36"/>
       <c r="U358" s="36"/>
       <c r="V358" s="9"/>
@@ -50083,7 +50082,7 @@
       <c r="P359" s="9"/>
       <c r="Q359" s="9"/>
       <c r="R359" s="9"/>
-      <c r="S359" s="46"/>
+      <c r="S359" s="45"/>
       <c r="T359" s="36"/>
       <c r="U359" s="36"/>
       <c r="V359" s="9"/>
@@ -50165,7 +50164,7 @@
       <c r="P360" s="9"/>
       <c r="Q360" s="9"/>
       <c r="R360" s="9"/>
-      <c r="S360" s="46"/>
+      <c r="S360" s="45"/>
       <c r="T360" s="36"/>
       <c r="U360" s="36"/>
       <c r="V360" s="9"/>
@@ -50247,7 +50246,7 @@
       <c r="P361" s="9"/>
       <c r="Q361" s="9"/>
       <c r="R361" s="9"/>
-      <c r="S361" s="46"/>
+      <c r="S361" s="45"/>
       <c r="T361" s="36"/>
       <c r="U361" s="36"/>
       <c r="V361" s="9"/>
@@ -50329,7 +50328,7 @@
       <c r="P362" s="9"/>
       <c r="Q362" s="9"/>
       <c r="R362" s="9"/>
-      <c r="S362" s="46"/>
+      <c r="S362" s="45"/>
       <c r="T362" s="36"/>
       <c r="U362" s="36"/>
       <c r="V362" s="9"/>
@@ -50411,7 +50410,7 @@
       <c r="P363" s="9"/>
       <c r="Q363" s="9"/>
       <c r="R363" s="9"/>
-      <c r="S363" s="46"/>
+      <c r="S363" s="45"/>
       <c r="T363" s="36"/>
       <c r="U363" s="36"/>
       <c r="V363" s="9"/>
@@ -50493,7 +50492,7 @@
       <c r="P364" s="9"/>
       <c r="Q364" s="9"/>
       <c r="R364" s="9"/>
-      <c r="S364" s="46"/>
+      <c r="S364" s="45"/>
       <c r="T364" s="36"/>
       <c r="U364" s="36"/>
       <c r="V364" s="9"/>
@@ -50575,7 +50574,7 @@
       <c r="P365" s="9"/>
       <c r="Q365" s="9"/>
       <c r="R365" s="9"/>
-      <c r="S365" s="46"/>
+      <c r="S365" s="45"/>
       <c r="T365" s="36"/>
       <c r="U365" s="36"/>
       <c r="V365" s="9"/>
@@ -50657,7 +50656,7 @@
       <c r="P366" s="9"/>
       <c r="Q366" s="9"/>
       <c r="R366" s="9"/>
-      <c r="S366" s="46"/>
+      <c r="S366" s="45"/>
       <c r="T366" s="36"/>
       <c r="U366" s="36"/>
       <c r="V366" s="9"/>
@@ -50739,7 +50738,7 @@
       <c r="P367" s="9"/>
       <c r="Q367" s="9"/>
       <c r="R367" s="9"/>
-      <c r="S367" s="46"/>
+      <c r="S367" s="45"/>
       <c r="T367" s="36"/>
       <c r="U367" s="36"/>
       <c r="V367" s="9"/>
@@ -50821,7 +50820,7 @@
       <c r="P368" s="9"/>
       <c r="Q368" s="9"/>
       <c r="R368" s="9"/>
-      <c r="S368" s="46"/>
+      <c r="S368" s="45"/>
       <c r="T368" s="36"/>
       <c r="U368" s="36"/>
       <c r="V368" s="9"/>
@@ -50903,7 +50902,7 @@
       <c r="P369" s="9"/>
       <c r="Q369" s="9"/>
       <c r="R369" s="9"/>
-      <c r="S369" s="46"/>
+      <c r="S369" s="45"/>
       <c r="T369" s="36"/>
       <c r="U369" s="36"/>
       <c r="V369" s="9"/>
@@ -50985,7 +50984,7 @@
       <c r="P370" s="9"/>
       <c r="Q370" s="9"/>
       <c r="R370" s="9"/>
-      <c r="S370" s="46"/>
+      <c r="S370" s="45"/>
       <c r="T370" s="36"/>
       <c r="U370" s="36"/>
       <c r="V370" s="9"/>
@@ -51067,7 +51066,7 @@
       <c r="P371" s="9"/>
       <c r="Q371" s="9"/>
       <c r="R371" s="9"/>
-      <c r="S371" s="46"/>
+      <c r="S371" s="45"/>
       <c r="T371" s="36"/>
       <c r="U371" s="36"/>
       <c r="V371" s="9"/>
@@ -51149,7 +51148,7 @@
       <c r="P372" s="9"/>
       <c r="Q372" s="9"/>
       <c r="R372" s="9"/>
-      <c r="S372" s="46"/>
+      <c r="S372" s="45"/>
       <c r="T372" s="36"/>
       <c r="U372" s="36"/>
       <c r="V372" s="9"/>
@@ -51231,7 +51230,7 @@
       <c r="P373" s="9"/>
       <c r="Q373" s="9"/>
       <c r="R373" s="9"/>
-      <c r="S373" s="46"/>
+      <c r="S373" s="45"/>
       <c r="T373" s="36"/>
       <c r="U373" s="36"/>
       <c r="V373" s="9"/>
@@ -51313,7 +51312,7 @@
       <c r="P374" s="9"/>
       <c r="Q374" s="9"/>
       <c r="R374" s="9"/>
-      <c r="S374" s="46"/>
+      <c r="S374" s="45"/>
       <c r="T374" s="36"/>
       <c r="U374" s="36"/>
       <c r="V374" s="9"/>
@@ -51395,7 +51394,7 @@
       <c r="P375" s="9"/>
       <c r="Q375" s="9"/>
       <c r="R375" s="9"/>
-      <c r="S375" s="46"/>
+      <c r="S375" s="45"/>
       <c r="T375" s="36"/>
       <c r="U375" s="36"/>
       <c r="V375" s="9"/>
@@ -51477,7 +51476,7 @@
       <c r="P376" s="9"/>
       <c r="Q376" s="9"/>
       <c r="R376" s="9"/>
-      <c r="S376" s="46"/>
+      <c r="S376" s="45"/>
       <c r="T376" s="36"/>
       <c r="U376" s="36"/>
       <c r="V376" s="9"/>
@@ -51559,7 +51558,7 @@
       <c r="P377" s="9"/>
       <c r="Q377" s="9"/>
       <c r="R377" s="9"/>
-      <c r="S377" s="46"/>
+      <c r="S377" s="45"/>
       <c r="T377" s="36"/>
       <c r="U377" s="36"/>
       <c r="V377" s="9"/>
@@ -51641,7 +51640,7 @@
       <c r="P378" s="9"/>
       <c r="Q378" s="9"/>
       <c r="R378" s="9"/>
-      <c r="S378" s="46"/>
+      <c r="S378" s="45"/>
       <c r="T378" s="36"/>
       <c r="U378" s="36"/>
       <c r="V378" s="9"/>
@@ -51723,7 +51722,7 @@
       <c r="P379" s="9"/>
       <c r="Q379" s="9"/>
       <c r="R379" s="9"/>
-      <c r="S379" s="46"/>
+      <c r="S379" s="45"/>
       <c r="T379" s="36"/>
       <c r="U379" s="36"/>
       <c r="V379" s="9"/>
@@ -51805,7 +51804,7 @@
       <c r="P380" s="9"/>
       <c r="Q380" s="9"/>
       <c r="R380" s="9"/>
-      <c r="S380" s="46"/>
+      <c r="S380" s="45"/>
       <c r="T380" s="36"/>
       <c r="U380" s="36"/>
       <c r="V380" s="9"/>
@@ -51887,7 +51886,7 @@
       <c r="P381" s="9"/>
       <c r="Q381" s="9"/>
       <c r="R381" s="9"/>
-      <c r="S381" s="46"/>
+      <c r="S381" s="45"/>
       <c r="T381" s="36"/>
       <c r="U381" s="36"/>
       <c r="V381" s="9"/>
@@ -51969,7 +51968,7 @@
       <c r="P382" s="9"/>
       <c r="Q382" s="9"/>
       <c r="R382" s="9"/>
-      <c r="S382" s="46"/>
+      <c r="S382" s="45"/>
       <c r="T382" s="36"/>
       <c r="U382" s="36"/>
       <c r="V382" s="9"/>
@@ -52051,7 +52050,7 @@
       <c r="P383" s="9"/>
       <c r="Q383" s="9"/>
       <c r="R383" s="9"/>
-      <c r="S383" s="46"/>
+      <c r="S383" s="45"/>
       <c r="T383" s="36"/>
       <c r="U383" s="36"/>
       <c r="V383" s="9"/>
@@ -52133,7 +52132,7 @@
       <c r="P384" s="9"/>
       <c r="Q384" s="9"/>
       <c r="R384" s="9"/>
-      <c r="S384" s="46"/>
+      <c r="S384" s="45"/>
       <c r="T384" s="36"/>
       <c r="U384" s="36"/>
       <c r="V384" s="9"/>
@@ -52215,7 +52214,7 @@
       <c r="P385" s="9"/>
       <c r="Q385" s="9"/>
       <c r="R385" s="9"/>
-      <c r="S385" s="46"/>
+      <c r="S385" s="45"/>
       <c r="T385" s="36"/>
       <c r="U385" s="36"/>
       <c r="V385" s="9"/>
@@ -52297,7 +52296,7 @@
       <c r="P386" s="9"/>
       <c r="Q386" s="9"/>
       <c r="R386" s="9"/>
-      <c r="S386" s="46"/>
+      <c r="S386" s="45"/>
       <c r="T386" s="36"/>
       <c r="U386" s="36"/>
       <c r="V386" s="9"/>
@@ -52379,7 +52378,7 @@
       <c r="P387" s="9"/>
       <c r="Q387" s="9"/>
       <c r="R387" s="9"/>
-      <c r="S387" s="46"/>
+      <c r="S387" s="45"/>
       <c r="T387" s="36"/>
       <c r="U387" s="36"/>
       <c r="V387" s="9"/>
@@ -52461,7 +52460,7 @@
       <c r="P388" s="9"/>
       <c r="Q388" s="9"/>
       <c r="R388" s="9"/>
-      <c r="S388" s="46"/>
+      <c r="S388" s="45"/>
       <c r="T388" s="36"/>
       <c r="U388" s="36"/>
       <c r="V388" s="9"/>
@@ -52543,7 +52542,7 @@
       <c r="P389" s="9"/>
       <c r="Q389" s="9"/>
       <c r="R389" s="9"/>
-      <c r="S389" s="46"/>
+      <c r="S389" s="45"/>
       <c r="T389" s="36"/>
       <c r="U389" s="36"/>
       <c r="V389" s="9"/>
@@ -52625,7 +52624,7 @@
       <c r="P390" s="9"/>
       <c r="Q390" s="9"/>
       <c r="R390" s="9"/>
-      <c r="S390" s="46"/>
+      <c r="S390" s="45"/>
       <c r="T390" s="36"/>
       <c r="U390" s="36"/>
       <c r="V390" s="9"/>
